--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/jul-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/jul-2026.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>79751</v>
+        <v>80508.55</v>
       </c>
     </row>
     <row r="3">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>482.28</v>
+        <v>486.86</v>
       </c>
     </row>
     <row r="4">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>8582.43</v>
+        <v>8663.950000000001</v>
       </c>
     </row>
     <row r="5">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>19270.79</v>
+        <v>19453.84</v>
       </c>
     </row>
     <row r="6">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>12761.18</v>
+        <v>12882.4</v>
       </c>
     </row>
     <row r="7">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>564.0599999999999</v>
+        <v>569.42</v>
       </c>
     </row>
     <row r="8">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>34462.24</v>
+        <v>34789.6</v>
       </c>
     </row>
     <row r="9">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>8183.77</v>
+        <v>8261.5</v>
       </c>
     </row>
     <row r="10">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>974.55</v>
+        <v>983.8099999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>8771.440000000001</v>
+        <v>8854.76</v>
       </c>
     </row>
     <row r="12">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>198.6</v>
+        <v>200.48</v>
       </c>
     </row>
     <row r="13">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4215.62</v>
+        <v>4255.67</v>
       </c>
     </row>
     <row r="14">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>8183.77</v>
+        <v>8261.5</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1752.96</v>
+        <v>1769.61</v>
       </c>
     </row>
     <row r="16">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>7731.95</v>
+        <v>7805.39</v>
       </c>
     </row>
     <row r="17">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>200.19</v>
+        <v>202.1</v>
       </c>
     </row>
     <row r="18">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>7727.71</v>
+        <v>7801.11</v>
       </c>
     </row>
     <row r="19">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>112.25</v>
+        <v>113.31</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>9267.74</v>
+        <v>9355.77</v>
       </c>
     </row>
     <row r="21">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>410.12</v>
+        <v>414.01</v>
       </c>
     </row>
     <row r="22">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>16335.92</v>
+        <v>16491.09</v>
       </c>
     </row>
     <row r="23">
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>115823.58</v>
+        <v>116275.71</v>
       </c>
     </row>
     <row r="24">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>8167.96</v>
+        <v>8199.84</v>
       </c>
     </row>
     <row r="25">
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1293.65</v>
+        <v>1298.7</v>
       </c>
     </row>
     <row r="26">
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>8310.719999999999</v>
+        <v>8343.16</v>
       </c>
     </row>
     <row r="27">
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>455.46</v>
+        <v>457.24</v>
       </c>
     </row>
     <row r="28">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>8362.889999999999</v>
+        <v>8395.530000000001</v>
       </c>
     </row>
     <row r="29">
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>447.2</v>
+        <v>448.94</v>
       </c>
     </row>
     <row r="30">
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>586.14</v>
+        <v>588.4299999999999</v>
       </c>
     </row>
     <row r="31">
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>7731.95</v>
+        <v>7762.13</v>
       </c>
     </row>
     <row r="32">
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>632.24</v>
+        <v>634.7</v>
       </c>
     </row>
     <row r="33">
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>205.22</v>
+        <v>206.02</v>
       </c>
     </row>
     <row r="34">
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>901.9</v>
+        <v>905.42</v>
       </c>
     </row>
     <row r="35">
@@ -2590,7 +2590,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>7654.7</v>
+        <v>7684.58</v>
       </c>
     </row>
     <row r="36">
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>296.9</v>
+        <v>298.06</v>
       </c>
     </row>
     <row r="37">
@@ -2712,7 +2712,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>8183.77</v>
+        <v>8215.709999999999</v>
       </c>
     </row>
     <row r="38">
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>488.67</v>
+        <v>490.58</v>
       </c>
     </row>
     <row r="39">
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>7654.7</v>
+        <v>7684.58</v>
       </c>
     </row>
     <row r="40">
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>3085.4</v>
+        <v>3097.45</v>
       </c>
     </row>
     <row r="41">
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>4697.2</v>
+        <v>4715.54</v>
       </c>
     </row>
     <row r="42">
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>7731.95</v>
+        <v>7762.13</v>
       </c>
     </row>
     <row r="43">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>24503.88</v>
+        <v>24750.33</v>
       </c>
     </row>
     <row r="44">
@@ -3139,7 +3139,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2058.26</v>
+        <v>2078.96</v>
       </c>
     </row>
     <row r="45">
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>8183.77</v>
+        <v>8266.08</v>
       </c>
     </row>
     <row r="46">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>445.01</v>
+        <v>449.49</v>
       </c>
     </row>
     <row r="47">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>7731.95</v>
+        <v>7809.71</v>
       </c>
     </row>
     <row r="48">
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>441.17</v>
+        <v>445.61</v>
       </c>
     </row>
     <row r="49">
@@ -3444,7 +3444,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>859.1799999999999</v>
+        <v>867.8200000000001</v>
       </c>
     </row>
     <row r="50">
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>441.17</v>
+        <v>445.61</v>
       </c>
     </row>
     <row r="51">
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>209.08</v>
+        <v>211.18</v>
       </c>
     </row>
     <row r="52">
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>8183.77</v>
+        <v>8266.08</v>
       </c>
     </row>
     <row r="53">
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>445.01</v>
+        <v>449.49</v>
       </c>
     </row>
     <row r="54">
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>701.72</v>
+        <v>708.78</v>
       </c>
     </row>
     <row r="55">
@@ -3810,7 +3810,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>7731.95</v>
+        <v>7809.71</v>
       </c>
     </row>
     <row r="56">
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>8487.040000000001</v>
+        <v>8572.4</v>
       </c>
     </row>
     <row r="57">
@@ -3932,7 +3932,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>654.1900000000001</v>
+        <v>660.77</v>
       </c>
     </row>
     <row r="58">
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>749.54</v>
+        <v>757.08</v>
       </c>
     </row>
     <row r="59">
@@ -4054,7 +4054,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>10735.04</v>
+        <v>10843.01</v>
       </c>
     </row>
     <row r="60">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>54821.01</v>
+        <v>55372.38</v>
       </c>
     </row>
     <row r="61">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>676.41</v>
+        <v>683.21</v>
       </c>
     </row>
     <row r="62">
@@ -4237,7 +4237,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>8167.96</v>
+        <v>8250.110000000001</v>
       </c>
     </row>
     <row r="63">
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>8310.719999999999</v>
+        <v>8394.299999999999</v>
       </c>
     </row>
     <row r="64">
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>4353.52</v>
+        <v>4397.31</v>
       </c>
     </row>
     <row r="65">
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>646.27</v>
+        <v>652.77</v>
       </c>
     </row>
     <row r="66">
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>764.04</v>
+        <v>771.73</v>
       </c>
     </row>
     <row r="67">
@@ -4542,7 +4542,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1672.5</v>
+        <v>1689.32</v>
       </c>
     </row>
     <row r="68">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>945.5</v>
+        <v>955.01</v>
       </c>
     </row>
     <row r="69">
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>8167.96</v>
+        <v>8250.110000000001</v>
       </c>
     </row>
     <row r="70">
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>715.8200000000001</v>
+        <v>723.02</v>
       </c>
     </row>
     <row r="71">
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>8113.98</v>
+        <v>8195.59</v>
       </c>
     </row>
     <row r="72">
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>10941.71</v>
+        <v>11051.75</v>
       </c>
     </row>
     <row r="73">
@@ -4908,7 +4908,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>10179.69</v>
+        <v>10282.07</v>
       </c>
     </row>
     <row r="74">
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>863.97</v>
+        <v>872.62</v>
       </c>
     </row>
     <row r="75">
@@ -5030,7 +5030,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>873.23</v>
+        <v>881.97</v>
       </c>
     </row>
     <row r="76">
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>8601.969999999999</v>
+        <v>8645.799999999999</v>
       </c>
     </row>
     <row r="77">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1521.33</v>
+        <v>1529.09</v>
       </c>
     </row>
     <row r="78">
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>36331.3</v>
+        <v>36516.43</v>
       </c>
     </row>
     <row r="79">
@@ -5274,7 +5274,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>2367.84</v>
+        <v>2379.9</v>
       </c>
     </row>
     <row r="80">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>9844.77</v>
+        <v>9894.940000000001</v>
       </c>
     </row>
     <row r="81">
@@ -5396,7 +5396,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>7720.54</v>
+        <v>7750.59</v>
       </c>
     </row>
     <row r="82">
@@ -5457,7 +5457,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>4217.67</v>
+        <v>4234.09</v>
       </c>
     </row>
     <row r="83">
@@ -5518,7 +5518,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1058.89</v>
+        <v>1063.02</v>
       </c>
     </row>
     <row r="84">
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1037.49</v>
+        <v>1041.53</v>
       </c>
     </row>
     <row r="85">
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1910.61</v>
+        <v>1918.05</v>
       </c>
     </row>
     <row r="86">
@@ -5701,7 +5701,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>8812.51</v>
+        <v>8846.82</v>
       </c>
     </row>
     <row r="87">
@@ -5762,7 +5762,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>495.42</v>
+        <v>497.35</v>
       </c>
     </row>
     <row r="88">
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2503.63</v>
+        <v>2490.94</v>
       </c>
     </row>
     <row r="89">
@@ -5884,7 +5884,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>7534.05</v>
+        <v>7495.89</v>
       </c>
     </row>
     <row r="90">
@@ -5945,7 +5945,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1171.96</v>
+        <v>1166.03</v>
       </c>
     </row>
     <row r="91">
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>8167.96</v>
+        <v>8126.58</v>
       </c>
     </row>
     <row r="92">
@@ -6067,7 +6067,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>8167.96</v>
+        <v>8126.58</v>
       </c>
     </row>
     <row r="93">
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>696.1799999999999</v>
+        <v>692.65</v>
       </c>
     </row>
     <row r="94">
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>671.22</v>
+        <v>667.8200000000001</v>
       </c>
     </row>
     <row r="95">
@@ -6250,7 +6250,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1841.66</v>
+        <v>1832.33</v>
       </c>
     </row>
     <row r="96">
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>8310.719999999999</v>
+        <v>8268.620000000001</v>
       </c>
     </row>
     <row r="97">
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>17257.47</v>
+        <v>17170.05</v>
       </c>
     </row>
     <row r="98">
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>8524.879999999999</v>
+        <v>8481.700000000001</v>
       </c>
     </row>
     <row r="99">
@@ -6494,7 +6494,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>8967.870000000001</v>
+        <v>8922.450000000001</v>
       </c>
     </row>
     <row r="100">
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>164.07</v>
+        <v>163.24</v>
       </c>
     </row>
     <row r="101">
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1142.79</v>
+        <v>1137.01</v>
       </c>
     </row>
     <row r="102">
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1738.44</v>
+        <v>1729.63</v>
       </c>
     </row>
     <row r="103">
@@ -6738,7 +6738,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>3348.98</v>
+        <v>3332.02</v>
       </c>
     </row>
     <row r="104">
@@ -6799,7 +6799,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>41235.28</v>
+        <v>41026.39</v>
       </c>
     </row>
     <row r="105">
@@ -6860,7 +6860,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>378.16</v>
+        <v>376.24</v>
       </c>
     </row>
     <row r="106">
@@ -6921,7 +6921,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>6203.31</v>
+        <v>6171.88</v>
       </c>
     </row>
     <row r="107">
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>445.01</v>
+        <v>442.76</v>
       </c>
     </row>
     <row r="108">
@@ -7043,7 +7043,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>442.83</v>
+        <v>440.58</v>
       </c>
     </row>
     <row r="109">
@@ -7104,7 +7104,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>164.08</v>
+        <v>163.25</v>
       </c>
     </row>
     <row r="110">
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>8113.98</v>
+        <v>8072.88</v>
       </c>
     </row>
     <row r="111">
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>16742.34</v>
+        <v>16657.53</v>
       </c>
     </row>
     <row r="112">
@@ -7287,7 +7287,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>593.51</v>
+        <v>590.5</v>
       </c>
     </row>
     <row r="113">
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>13907.22</v>
+        <v>13836.77</v>
       </c>
     </row>
     <row r="114">
@@ -7409,7 +7409,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>7720.54</v>
+        <v>7681.43</v>
       </c>
     </row>
     <row r="115">
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>385.65</v>
+        <v>383.7</v>
       </c>
     </row>
     <row r="116">
@@ -7531,7 +7531,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>8117.61</v>
+        <v>8076.49</v>
       </c>
     </row>
     <row r="117">
@@ -7592,7 +7592,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>614.0599999999999</v>
+        <v>615.37</v>
       </c>
     </row>
     <row r="118">
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>5160.37</v>
+        <v>5171.37</v>
       </c>
     </row>
     <row r="119">
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1122.34</v>
+        <v>1124.73</v>
       </c>
     </row>
     <row r="120">
@@ -7775,7 +7775,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>7731.13</v>
+        <v>7747.61</v>
       </c>
     </row>
     <row r="121">
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1233.99</v>
+        <v>1236.62</v>
       </c>
     </row>
     <row r="122">
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>8113.98</v>
+        <v>8131.27</v>
       </c>
     </row>
     <row r="123">
@@ -7958,7 +7958,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>154.25</v>
+        <v>154.58</v>
       </c>
     </row>
     <row r="124">
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>2319.34</v>
+        <v>2324.28</v>
       </c>
     </row>
     <row r="125">
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>1162.09</v>
+        <v>1164.57</v>
       </c>
     </row>
     <row r="126">
@@ -8141,7 +8141,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>8113.98</v>
+        <v>8131.27</v>
       </c>
     </row>
     <row r="127">
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>6264.61</v>
+        <v>6277.96</v>
       </c>
     </row>
     <row r="128">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>21768.56</v>
+        <v>21814.95</v>
       </c>
     </row>
     <row r="129">
@@ -8324,7 +8324,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>2799.67</v>
+        <v>2805.64</v>
       </c>
     </row>
     <row r="130">
@@ -8385,7 +8385,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>8113.98</v>
+        <v>8166.88</v>
       </c>
     </row>
     <row r="131">
@@ -8446,7 +8446,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>261.01</v>
+        <v>262.71</v>
       </c>
     </row>
     <row r="132">
@@ -8507,7 +8507,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>8310.719999999999</v>
+        <v>8364.9</v>
       </c>
     </row>
     <row r="133">
@@ -8568,7 +8568,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>631.6799999999999</v>
+        <v>635.8</v>
       </c>
     </row>
     <row r="134">
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>200.19</v>
+        <v>201.5</v>
       </c>
     </row>
     <row r="135">
@@ -8690,7 +8690,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>21765.71</v>
+        <v>21907.61</v>
       </c>
     </row>
     <row r="136">
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2827.61</v>
+        <v>2846.04</v>
       </c>
     </row>
     <row r="137">
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>14913.8</v>
+        <v>15011.03</v>
       </c>
     </row>
     <row r="138">
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>477.89</v>
+        <v>481.01</v>
       </c>
     </row>
     <row r="139">
@@ -8934,7 +8934,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>7731.95</v>
+        <v>7782.35</v>
       </c>
     </row>
     <row r="140">
@@ -8995,7 +8995,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>2922.05</v>
+        <v>2941.1</v>
       </c>
     </row>
     <row r="141">
@@ -9056,7 +9056,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>603.61</v>
+        <v>607.55</v>
       </c>
     </row>
     <row r="142">
@@ -9117,7 +9117,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>145.72</v>
+        <v>146.67</v>
       </c>
     </row>
     <row r="143">
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>10443.05</v>
+        <v>10511.13</v>
       </c>
     </row>
     <row r="144">
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>8167.96</v>
+        <v>8221.209999999999</v>
       </c>
     </row>
     <row r="145">
@@ -9300,7 +9300,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>7082.58</v>
+        <v>7128.76</v>
       </c>
     </row>
     <row r="146">
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>20035.38</v>
+        <v>20165.99</v>
       </c>
     </row>
     <row r="147">
@@ -9422,7 +9422,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>8310.719999999999</v>
+        <v>8364.9</v>
       </c>
     </row>
     <row r="148">
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1038.99</v>
+        <v>1045.76</v>
       </c>
     </row>
     <row r="149">
@@ -9544,7 +9544,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1229.26</v>
+        <v>1237.28</v>
       </c>
     </row>
     <row r="150">
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>164.07</v>
+        <v>165.14</v>
       </c>
     </row>
     <row r="151">
@@ -9666,7 +9666,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>7720.54</v>
+        <v>7770.87</v>
       </c>
     </row>
     <row r="152">
@@ -9727,7 +9727,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>8812.51</v>
+        <v>8869.969999999999</v>
       </c>
     </row>
     <row r="153">
@@ -9788,7 +9788,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>20797.88</v>
+        <v>20845.58</v>
       </c>
     </row>
     <row r="154">
@@ -9849,7 +9849,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>10009.36</v>
+        <v>10032.31</v>
       </c>
     </row>
     <row r="155">
@@ -9910,7 +9910,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1639.31</v>
+        <v>1643.07</v>
       </c>
     </row>
     <row r="156">
@@ -9971,7 +9971,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>11649.65</v>
+        <v>11676.37</v>
       </c>
     </row>
     <row r="157">
@@ -10032,7 +10032,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>1054.47</v>
+        <v>1056.89</v>
       </c>
     </row>
     <row r="158">
@@ -10093,7 +10093,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>13629.77</v>
+        <v>13661.03</v>
       </c>
     </row>
     <row r="159">
@@ -10154,7 +10154,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>3856.33</v>
+        <v>3865.17</v>
       </c>
     </row>
     <row r="160">
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>509.47</v>
+        <v>510.64</v>
       </c>
     </row>
     <row r="161">
@@ -10276,7 +10276,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>5083.8</v>
+        <v>5095.46</v>
       </c>
     </row>
     <row r="162">
@@ -10337,7 +10337,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>1553.06</v>
+        <v>1556.62</v>
       </c>
     </row>
     <row r="163">
@@ -10398,7 +10398,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>4090.36</v>
+        <v>4099.74</v>
       </c>
     </row>
     <row r="164">
@@ -10459,7 +10459,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1763.69</v>
+        <v>1767.73</v>
       </c>
     </row>
     <row r="165">
@@ -10520,7 +10520,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>962.51</v>
+        <v>964.72</v>
       </c>
     </row>
     <row r="166">
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>1438.02</v>
+        <v>1441.31</v>
       </c>
     </row>
     <row r="167">
@@ -10642,7 +10642,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>3725.93</v>
+        <v>3734.48</v>
       </c>
     </row>
     <row r="168">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>29668.01</v>
+        <v>29736.05</v>
       </c>
     </row>
     <row r="169">
@@ -10764,7 +10764,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>1423.64</v>
+        <v>1426.9</v>
       </c>
     </row>
     <row r="170">
@@ -10825,7 +10825,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>9398.780000000001</v>
+        <v>9420.34</v>
       </c>
     </row>
     <row r="171">
@@ -10886,7 +10886,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>2381.75</v>
+        <v>2387.21</v>
       </c>
     </row>
     <row r="172">
@@ -10947,7 +10947,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>34163.82</v>
+        <v>34242.16</v>
       </c>
     </row>
     <row r="173">
@@ -11008,7 +11008,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>8959.99</v>
+        <v>8980.540000000001</v>
       </c>
     </row>
     <row r="174">
@@ -11069,7 +11069,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>562.3</v>
+        <v>563.59</v>
       </c>
     </row>
     <row r="175">
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>455.65</v>
+        <v>456.7</v>
       </c>
     </row>
     <row r="176">
@@ -11191,7 +11191,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>8757.860000000001</v>
+        <v>8777.950000000001</v>
       </c>
     </row>
     <row r="177">
@@ -11252,7 +11252,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>24582.6</v>
+        <v>24638.98</v>
       </c>
     </row>
     <row r="178">
@@ -11313,7 +11313,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>3170.58</v>
+        <v>3177.85</v>
       </c>
     </row>
     <row r="179">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>8310.719999999999</v>
+        <v>8329.780000000001</v>
       </c>
     </row>
     <row r="180">
@@ -11435,7 +11435,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>6552.79</v>
+        <v>6567.82</v>
       </c>
     </row>
     <row r="181">
@@ -11496,7 +11496,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>22177.49</v>
+        <v>22228.35</v>
       </c>
     </row>
     <row r="182">
@@ -11557,7 +11557,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>6505.47</v>
+        <v>6520.38</v>
       </c>
     </row>
     <row r="183">
@@ -11618,7 +11618,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>3906.73</v>
+        <v>3915.69</v>
       </c>
     </row>
     <row r="184">
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>30559.88</v>
+        <v>30629.96</v>
       </c>
     </row>
     <row r="185">
@@ -11740,7 +11740,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>12312.28</v>
+        <v>12340.51</v>
       </c>
     </row>
     <row r="186">
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>2656.83</v>
+        <v>2662.92</v>
       </c>
     </row>
     <row r="187">
@@ -11862,7 +11862,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>385.92</v>
+        <v>386.8</v>
       </c>
     </row>
     <row r="188">
@@ -11923,7 +11923,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>20540.11</v>
+        <v>20587.22</v>
       </c>
     </row>
     <row r="189">
@@ -11984,7 +11984,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>4409.21</v>
+        <v>4438.73</v>
       </c>
     </row>
     <row r="190">
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>2352.72</v>
+        <v>2368.47</v>
       </c>
     </row>
     <row r="191">
@@ -12106,7 +12106,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>639.17</v>
+        <v>643.45</v>
       </c>
     </row>
     <row r="192">
@@ -12167,7 +12167,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>34924.15</v>
+        <v>35157.91</v>
       </c>
     </row>
     <row r="193">
@@ -12228,7 +12228,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>7731.13</v>
+        <v>7782.88</v>
       </c>
     </row>
     <row r="194">
@@ -12289,7 +12289,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>8040.11</v>
+        <v>8093.93</v>
       </c>
     </row>
     <row r="195">
@@ -12350,7 +12350,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>15165.77</v>
+        <v>15267.28</v>
       </c>
     </row>
     <row r="196">
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>16114.92</v>
+        <v>16222.79</v>
       </c>
     </row>
     <row r="197">
@@ -12472,7 +12472,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>1146.55</v>
+        <v>1154.23</v>
       </c>
     </row>
     <row r="198">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>1811.12</v>
+        <v>1823.24</v>
       </c>
     </row>
     <row r="199">
@@ -12594,7 +12594,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>2176.57</v>
+        <v>2191.14</v>
       </c>
     </row>
     <row r="200">
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>554.14</v>
+        <v>557.85</v>
       </c>
     </row>
     <row r="201">
@@ -12716,7 +12716,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>1260.34</v>
+        <v>1268.78</v>
       </c>
     </row>
     <row r="202">
@@ -12777,7 +12777,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>2428.65</v>
+        <v>2444.91</v>
       </c>
     </row>
     <row r="203">
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>480.86</v>
+        <v>484.08</v>
       </c>
     </row>
     <row r="204">
@@ -12899,7 +12899,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>6891.47</v>
+        <v>6937.6</v>
       </c>
     </row>
     <row r="205">
@@ -12960,7 +12960,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>8117.61</v>
+        <v>8171.95</v>
       </c>
     </row>
     <row r="206">
@@ -13021,7 +13021,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>2914.38</v>
+        <v>2933.89</v>
       </c>
     </row>
     <row r="207">
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>1736.46</v>
+        <v>1748.08</v>
       </c>
     </row>
     <row r="208">
@@ -13143,7 +13143,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>10708.87</v>
+        <v>10780.55</v>
       </c>
     </row>
     <row r="209">
@@ -13204,7 +13204,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>2012.03</v>
+        <v>2025.5</v>
       </c>
     </row>
     <row r="210">
@@ -13265,7 +13265,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>6499.71</v>
+        <v>6543.21</v>
       </c>
     </row>
     <row r="211">
@@ -13326,7 +13326,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>18968.74</v>
+        <v>19095.71</v>
       </c>
     </row>
     <row r="212">
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>88.14</v>
+        <v>88.73</v>
       </c>
     </row>
     <row r="213">
@@ -13448,7 +13448,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>3292.16</v>
+        <v>3314.2</v>
       </c>
     </row>
     <row r="214">
@@ -13509,7 +13509,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>19628.09</v>
+        <v>19759.47</v>
       </c>
     </row>
     <row r="215">
@@ -13570,7 +13570,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>272.17</v>
+        <v>273.99</v>
       </c>
     </row>
     <row r="216">
@@ -13631,7 +13631,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>3804.99</v>
+        <v>3830.46</v>
       </c>
     </row>
     <row r="217">
@@ -13692,7 +13692,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>385</v>
+        <v>387.58</v>
       </c>
     </row>
     <row r="218">
@@ -13753,7 +13753,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>1085.35</v>
+        <v>1092.62</v>
       </c>
     </row>
     <row r="219">
@@ -13814,7 +13814,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>7190.85</v>
+        <v>7238.98</v>
       </c>
     </row>
     <row r="220">
@@ -13875,7 +13875,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>11418.04</v>
+        <v>11494.47</v>
       </c>
     </row>
     <row r="221">
@@ -13936,7 +13936,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>7731.95</v>
+        <v>7783.7</v>
       </c>
     </row>
     <row r="222">
@@ -13997,7 +13997,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>200.19</v>
+        <v>201.53</v>
       </c>
     </row>
     <row r="223">
@@ -14058,7 +14058,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>2831.32</v>
+        <v>2850.28</v>
       </c>
     </row>
     <row r="224">
@@ -14119,7 +14119,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>8183.77</v>
+        <v>8238.549999999999</v>
       </c>
     </row>
     <row r="225">
@@ -14180,7 +14180,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>11136.19</v>
+        <v>11210.73</v>
       </c>
     </row>
     <row r="226">
@@ -14241,7 +14241,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>313.11</v>
+        <v>315.21</v>
       </c>
     </row>
     <row r="227">
@@ -14302,7 +14302,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>3348.57</v>
+        <v>3370.98</v>
       </c>
     </row>
     <row r="228">
@@ -14363,7 +14363,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>1014.83</v>
+        <v>1021.63</v>
       </c>
     </row>
     <row r="229">
@@ -14424,7 +14424,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>2563.76</v>
+        <v>2580.92</v>
       </c>
     </row>
     <row r="230">
@@ -14485,7 +14485,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>8335.32</v>
+        <v>8391.110000000001</v>
       </c>
     </row>
     <row r="231">
@@ -14546,7 +14546,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>8117.69</v>
+        <v>8172.02</v>
       </c>
     </row>
     <row r="232">
@@ -14607,7 +14607,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>8113.98</v>
+        <v>8168.29</v>
       </c>
     </row>
     <row r="233">
@@ -14668,7 +14668,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>4707.26</v>
+        <v>4738.77</v>
       </c>
     </row>
     <row r="234">
@@ -14729,7 +14729,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>1118.41</v>
+        <v>1125.89</v>
       </c>
     </row>
     <row r="235">
@@ -14790,7 +14790,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>8117.69</v>
+        <v>8172.02</v>
       </c>
     </row>
     <row r="236">
@@ -14851,7 +14851,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>52632.03</v>
+        <v>52984.33</v>
       </c>
     </row>
     <row r="237">
@@ -14912,7 +14912,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>11152.23</v>
+        <v>11226.88</v>
       </c>
     </row>
     <row r="238">
@@ -14973,7 +14973,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>3276.44</v>
+        <v>3298.37</v>
       </c>
     </row>
     <row r="239">
@@ -15034,7 +15034,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>362.77</v>
+        <v>365.2</v>
       </c>
     </row>
     <row r="240">
@@ -15095,7 +15095,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>96.02</v>
+        <v>96.66</v>
       </c>
     </row>
     <row r="241">
@@ -15156,7 +15156,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>8117.69</v>
+        <v>8172.02</v>
       </c>
     </row>
     <row r="242">
@@ -15217,7 +15217,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>1286.84</v>
+        <v>1295.45</v>
       </c>
     </row>
     <row r="243">
@@ -15278,7 +15278,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>876.87</v>
+        <v>882.74</v>
       </c>
     </row>
     <row r="244">
@@ -15339,7 +15339,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>3591.74</v>
+        <v>3615.78</v>
       </c>
     </row>
     <row r="245">
@@ -15400,7 +15400,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>1685.43</v>
+        <v>1696.71</v>
       </c>
     </row>
     <row r="246">
@@ -15461,7 +15461,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>15193.25</v>
+        <v>15294.94</v>
       </c>
     </row>
     <row r="247">
@@ -15522,7 +15522,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>388.22</v>
+        <v>390.81</v>
       </c>
     </row>
     <row r="248">
@@ -15583,7 +15583,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>15447.18</v>
+        <v>15550.58</v>
       </c>
     </row>
     <row r="249">
@@ -15644,7 +15644,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>1273.28</v>
+        <v>1281.8</v>
       </c>
     </row>
     <row r="250">
@@ -15705,7 +15705,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>11664.17</v>
+        <v>11742.24</v>
       </c>
     </row>
     <row r="251">
@@ -15766,7 +15766,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>5341.12</v>
+        <v>5376.88</v>
       </c>
     </row>
     <row r="252">
@@ -15827,7 +15827,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>13912.84</v>
+        <v>14005.96</v>
       </c>
     </row>
     <row r="253">
@@ -15888,7 +15888,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>10123.63</v>
+        <v>10191.4</v>
       </c>
     </row>
     <row r="254">
@@ -15949,7 +15949,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>2012.7</v>
+        <v>2026.78</v>
       </c>
     </row>
     <row r="255">
@@ -16010,7 +16010,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>7279.57</v>
+        <v>7330.51</v>
       </c>
     </row>
     <row r="256">
@@ -16071,7 +16071,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>8338.1</v>
+        <v>8396.450000000001</v>
       </c>
     </row>
     <row r="257">
@@ -16132,7 +16132,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>8117.61</v>
+        <v>8174.42</v>
       </c>
     </row>
     <row r="258">
@@ -16193,7 +16193,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>11292.31</v>
+        <v>11371.34</v>
       </c>
     </row>
     <row r="259">
@@ -16254,7 +16254,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>475.75</v>
+        <v>479.08</v>
       </c>
     </row>
     <row r="260">
@@ -16315,7 +16315,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>4601.65</v>
+        <v>4633.86</v>
       </c>
     </row>
     <row r="261">
@@ -16376,7 +16376,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>627.99</v>
+        <v>632.39</v>
       </c>
     </row>
     <row r="262">
@@ -16437,7 +16437,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>3730.99</v>
+        <v>3757.1</v>
       </c>
     </row>
     <row r="263">
@@ -16498,7 +16498,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>713.16</v>
+        <v>718.15</v>
       </c>
     </row>
     <row r="264">
@@ -16559,7 +16559,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>7731.13</v>
+        <v>7785.23</v>
       </c>
     </row>
     <row r="265">
@@ -16620,7 +16620,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>30331.53</v>
+        <v>30543.81</v>
       </c>
     </row>
     <row r="266">
@@ -16681,7 +16681,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>8990.48</v>
+        <v>9053.4</v>
       </c>
     </row>
     <row r="267">
@@ -16742,7 +16742,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>723.45</v>
+        <v>728.51</v>
       </c>
     </row>
     <row r="268">
@@ -16803,7 +16803,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>7731.13</v>
+        <v>7785.23</v>
       </c>
     </row>
     <row r="269">
@@ -16864,7 +16864,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>2149.78</v>
+        <v>2164.82</v>
       </c>
     </row>
     <row r="270">
@@ -16925,7 +16925,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>8117.61</v>
+        <v>8174.42</v>
       </c>
     </row>
     <row r="271">
@@ -16986,7 +16986,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>9398.76</v>
+        <v>9464.540000000001</v>
       </c>
     </row>
     <row r="272">
@@ -17047,7 +17047,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>9609.34</v>
+        <v>9676.59</v>
       </c>
     </row>
     <row r="273">
@@ -17108,7 +17108,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>8117.69</v>
+        <v>8174.5</v>
       </c>
     </row>
     <row r="274">
@@ -17169,7 +17169,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>1782.05</v>
+        <v>1794.53</v>
       </c>
     </row>
     <row r="275">
@@ -17230,7 +17230,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>6953.61</v>
+        <v>7002.27</v>
       </c>
     </row>
     <row r="276">
@@ -17291,7 +17291,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>7280.06</v>
+        <v>7331.01</v>
       </c>
     </row>
     <row r="277">
@@ -17352,7 +17352,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>7013.67</v>
+        <v>7062.75</v>
       </c>
     </row>
     <row r="278">
@@ -17413,7 +17413,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>2903.64</v>
+        <v>2923.96</v>
       </c>
     </row>
     <row r="279">
@@ -17474,7 +17474,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>4901.65</v>
+        <v>4935.96</v>
       </c>
     </row>
     <row r="280">
@@ -17535,7 +17535,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>13069.71</v>
+        <v>13161.18</v>
       </c>
     </row>
     <row r="281">
@@ -17596,7 +17596,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>9146.889999999999</v>
+        <v>9210.9</v>
       </c>
     </row>
     <row r="282">
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>14699.72</v>
+        <v>14802.6</v>
       </c>
     </row>
     <row r="283">
@@ -17718,7 +17718,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>14523.67</v>
+        <v>14625.31</v>
       </c>
     </row>
     <row r="284">
@@ -17779,7 +17779,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>37529.03</v>
+        <v>37791.67</v>
       </c>
     </row>
     <row r="285">
@@ -17840,7 +17840,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>35268.44</v>
+        <v>35515.26</v>
       </c>
     </row>
     <row r="286">
@@ -17901,7 +17901,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>274.92</v>
+        <v>276.84</v>
       </c>
     </row>
     <row r="287">
@@ -17962,7 +17962,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>4869.58</v>
+        <v>4903.66</v>
       </c>
     </row>
     <row r="288">
@@ -18023,7 +18023,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>1596.42</v>
+        <v>1607.59</v>
       </c>
     </row>
     <row r="289">
@@ -18084,7 +18084,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>681.05</v>
+        <v>685.8200000000001</v>
       </c>
     </row>
     <row r="290">
@@ -18145,7 +18145,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>1667.59</v>
+        <v>1679.26</v>
       </c>
     </row>
     <row r="291">
@@ -18206,7 +18206,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>756.85</v>
+        <v>762.15</v>
       </c>
     </row>
     <row r="292">
@@ -18267,7 +18267,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>621.59</v>
+        <v>625.9400000000001</v>
       </c>
     </row>
     <row r="293">
@@ -18328,7 +18328,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>1176.98</v>
+        <v>1185.22</v>
       </c>
     </row>
     <row r="294">
@@ -18389,7 +18389,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>31582.66</v>
+        <v>31803.69</v>
       </c>
     </row>
     <row r="295">
@@ -18450,7 +18450,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>5198.22</v>
+        <v>5234.6</v>
       </c>
     </row>
     <row r="296">
@@ -18511,7 +18511,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>8028.14</v>
+        <v>8084.33</v>
       </c>
     </row>
     <row r="297">
@@ -18572,7 +18572,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>11744.57</v>
+        <v>11826.76</v>
       </c>
     </row>
     <row r="298">
@@ -18633,7 +18633,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>17106.64</v>
+        <v>17226.36</v>
       </c>
     </row>
     <row r="299">
@@ -18694,7 +18694,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>4226.54</v>
+        <v>4256.12</v>
       </c>
     </row>
     <row r="300">
@@ -18755,7 +18755,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>1431.01</v>
+        <v>1441.03</v>
       </c>
     </row>
     <row r="301">
@@ -18816,7 +18816,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>6642.9</v>
+        <v>6689.39</v>
       </c>
     </row>
     <row r="302">
@@ -18877,7 +18877,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>3016.41</v>
+        <v>3037.52</v>
       </c>
     </row>
     <row r="303">
@@ -18938,7 +18938,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>18180.74</v>
+        <v>18307.98</v>
       </c>
     </row>
     <row r="304">
@@ -18999,7 +18999,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>440.14</v>
+        <v>443.22</v>
       </c>
     </row>
     <row r="305">
@@ -19060,7 +19060,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>650.6900000000001</v>
+        <v>655.24</v>
       </c>
     </row>
     <row r="306">
@@ -19121,7 +19121,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>44.07</v>
+        <v>44.38</v>
       </c>
     </row>
     <row r="307">
@@ -19182,7 +19182,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>1339.39</v>
+        <v>1348.76</v>
       </c>
     </row>
     <row r="308">
@@ -19243,7 +19243,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>995.08</v>
+        <v>1002.04</v>
       </c>
     </row>
     <row r="309">
@@ -19304,7 +19304,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>404.21</v>
+        <v>407.04</v>
       </c>
     </row>
     <row r="310">
@@ -19365,7 +19365,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>3429.03</v>
+        <v>3453.03</v>
       </c>
     </row>
     <row r="311">
@@ -19426,7 +19426,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>8117.61</v>
+        <v>8174.42</v>
       </c>
     </row>
     <row r="312">
@@ -19487,7 +19487,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>15467.63</v>
+        <v>15575.88</v>
       </c>
     </row>
     <row r="313">
@@ -19548,7 +19548,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>1113.26</v>
+        <v>1121.05</v>
       </c>
     </row>
     <row r="314">
@@ -19609,7 +19609,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>528.13</v>
+        <v>531.83</v>
       </c>
     </row>
     <row r="315">
@@ -19670,7 +19670,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>59117.71</v>
+        <v>59531.44</v>
       </c>
     </row>
     <row r="316">
@@ -19731,7 +19731,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>7731.13</v>
+        <v>7785.23</v>
       </c>
     </row>
     <row r="317">
@@ -19792,7 +19792,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>38443.33</v>
+        <v>38712.37</v>
       </c>
     </row>
     <row r="318">
@@ -19853,7 +19853,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>8218.040000000001</v>
+        <v>8275.549999999999</v>
       </c>
     </row>
     <row r="319">
@@ -19914,7 +19914,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>7731.95</v>
+        <v>7786.06</v>
       </c>
     </row>
     <row r="320">
@@ -19975,7 +19975,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>302.82</v>
+        <v>304.93</v>
       </c>
     </row>
     <row r="321">
@@ -20036,7 +20036,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>21052.81</v>
+        <v>21200.15</v>
       </c>
     </row>
     <row r="322">
@@ -20097,7 +20097,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>979.08</v>
+        <v>985.9299999999999</v>
       </c>
     </row>
     <row r="323">
@@ -20158,7 +20158,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>9855.16</v>
+        <v>9924.129999999999</v>
       </c>
     </row>
     <row r="324">
@@ -20219,7 +20219,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>21482.56</v>
+        <v>21632.9</v>
       </c>
     </row>
     <row r="325">
@@ -20280,7 +20280,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>4054.13</v>
+        <v>4082.5</v>
       </c>
     </row>
     <row r="326">
@@ -20341,7 +20341,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>16260.4</v>
+        <v>16374.19</v>
       </c>
     </row>
     <row r="327">
@@ -20402,7 +20402,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>6106.33</v>
+        <v>6149.06</v>
       </c>
     </row>
     <row r="328">
@@ -20463,7 +20463,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>889.92</v>
+        <v>896.15</v>
       </c>
     </row>
     <row r="329">
@@ -20524,7 +20524,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>50155.82</v>
+        <v>50506.83</v>
       </c>
     </row>
     <row r="330">
@@ -20585,7 +20585,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>8117.61</v>
+        <v>8174.42</v>
       </c>
     </row>
     <row r="331">
@@ -20646,7 +20646,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>38384.17</v>
+        <v>38652.79</v>
       </c>
     </row>
     <row r="332">
@@ -20707,7 +20707,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>2899.48</v>
+        <v>2919.77</v>
       </c>
     </row>
     <row r="333">
@@ -20768,7 +20768,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>2547.31</v>
+        <v>2565.14</v>
       </c>
     </row>
     <row r="334">
@@ -20829,7 +20829,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>2899.48</v>
+        <v>2919.77</v>
       </c>
     </row>
     <row r="335">
@@ -20890,7 +20890,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>2547.31</v>
+        <v>2565.14</v>
       </c>
     </row>
     <row r="336">
@@ -20951,7 +20951,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>2608.25</v>
+        <v>2626.5</v>
       </c>
     </row>
     <row r="337">
@@ -21012,7 +21012,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>6805.89</v>
+        <v>6853.52</v>
       </c>
     </row>
     <row r="338">
@@ -21073,7 +21073,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>2449.6</v>
+        <v>2466.74</v>
       </c>
     </row>
     <row r="339">
@@ -21134,7 +21134,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>44894.94</v>
+        <v>45209.14</v>
       </c>
     </row>
     <row r="340">
@@ -21195,7 +21195,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>2547.31</v>
+        <v>2565.14</v>
       </c>
     </row>
     <row r="341">
@@ -21256,7 +21256,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>2547.31</v>
+        <v>2565.14</v>
       </c>
     </row>
     <row r="342">
@@ -21317,7 +21317,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>1133.45</v>
+        <v>1141.38</v>
       </c>
     </row>
     <row r="343">
@@ -21378,7 +21378,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>47940.78</v>
+        <v>48276.29</v>
       </c>
     </row>
     <row r="344">
@@ -21439,7 +21439,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>4566.68</v>
+        <v>4598.64</v>
       </c>
     </row>
     <row r="345">
@@ -21500,7 +21500,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>12426.19</v>
+        <v>12513.15</v>
       </c>
     </row>
     <row r="346">
@@ -21561,7 +21561,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>3790.52</v>
+        <v>3817.05</v>
       </c>
     </row>
     <row r="347">
@@ -21622,7 +21622,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>11015.05</v>
+        <v>11092.13</v>
       </c>
     </row>
     <row r="348">
@@ -21683,7 +21683,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>503.03</v>
+        <v>506.55</v>
       </c>
     </row>
     <row r="349">
@@ -21744,7 +21744,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>4856.28</v>
+        <v>4890.26</v>
       </c>
     </row>
     <row r="350">
@@ -21805,7 +21805,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>7195.56</v>
+        <v>7245.92</v>
       </c>
     </row>
     <row r="351">
@@ -21866,7 +21866,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>7547.48</v>
+        <v>7600.3</v>
       </c>
     </row>
     <row r="352">
@@ -21927,7 +21927,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>13393.88</v>
+        <v>13487.61</v>
       </c>
     </row>
     <row r="353">
@@ -21988,7 +21988,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>18738.97</v>
+        <v>18870.11</v>
       </c>
     </row>
     <row r="354">
@@ -22049,7 +22049,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>1667.59</v>
+        <v>1679.26</v>
       </c>
     </row>
     <row r="355">
@@ -22110,7 +22110,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>210.68</v>
+        <v>212.15</v>
       </c>
     </row>
     <row r="356">
@@ -22171,7 +22171,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>230.82</v>
+        <v>232.44</v>
       </c>
     </row>
     <row r="357">
@@ -22232,7 +22232,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>1886.84</v>
+        <v>1900.05</v>
       </c>
     </row>
     <row r="358">
@@ -22293,7 +22293,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>838.08</v>
+        <v>843.95</v>
       </c>
     </row>
     <row r="359">
@@ -22354,7 +22354,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>2155.06</v>
+        <v>2170.14</v>
       </c>
     </row>
     <row r="360">
@@ -22415,7 +22415,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>1844.71</v>
+        <v>1857.62</v>
       </c>
     </row>
     <row r="361">
@@ -22476,7 +22476,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>12369.1</v>
+        <v>12455.66</v>
       </c>
     </row>
     <row r="362">
@@ -22537,7 +22537,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>9717.33</v>
+        <v>9785.33</v>
       </c>
     </row>
     <row r="363">
@@ -22598,7 +22598,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>24738.2</v>
+        <v>24911.33</v>
       </c>
     </row>
     <row r="364">
@@ -22659,7 +22659,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>9820.629999999999</v>
+        <v>9889.360000000001</v>
       </c>
     </row>
     <row r="365">
@@ -22720,7 +22720,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>2899.48</v>
+        <v>2919.77</v>
       </c>
     </row>
     <row r="366">
@@ -22781,7 +22781,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>6155.04</v>
+        <v>6198.12</v>
       </c>
     </row>
     <row r="367">
@@ -22842,7 +22842,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>12369.1</v>
+        <v>12455.66</v>
       </c>
     </row>
     <row r="368">
@@ -22903,7 +22903,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>6155.04</v>
+        <v>6198.12</v>
       </c>
     </row>
     <row r="369">
@@ -22964,7 +22964,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>10644.84</v>
+        <v>10719.34</v>
       </c>
     </row>
     <row r="370">
@@ -23025,7 +23025,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>2899.48</v>
+        <v>2919.77</v>
       </c>
     </row>
     <row r="371">
@@ -23086,7 +23086,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>1676.16</v>
+        <v>1687.89</v>
       </c>
     </row>
     <row r="372">
@@ -23147,7 +23147,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>18748.99</v>
+        <v>18880.2</v>
       </c>
     </row>
     <row r="373">
@@ -23208,7 +23208,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>2899.48</v>
+        <v>2919.77</v>
       </c>
     </row>
     <row r="374">
@@ -23269,7 +23269,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>7747.18</v>
+        <v>7801.39</v>
       </c>
     </row>
     <row r="375">
@@ -23330,7 +23330,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>36936.84</v>
+        <v>37195.34</v>
       </c>
     </row>
     <row r="376">
@@ -23391,7 +23391,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>15660.04</v>
+        <v>15769.63</v>
       </c>
     </row>
     <row r="377">
@@ -23452,7 +23452,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>72484.61</v>
+        <v>72991.88</v>
       </c>
     </row>
     <row r="378">
@@ -23513,7 +23513,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>36076.03</v>
+        <v>36328.51</v>
       </c>
     </row>
     <row r="379">
@@ -23574,7 +23574,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>38077.73</v>
+        <v>38344.21</v>
       </c>
     </row>
     <row r="380">
@@ -23635,7 +23635,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>4940.08</v>
+        <v>4974.65</v>
       </c>
     </row>
     <row r="381">
@@ -23696,7 +23696,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>4641.25</v>
+        <v>4673.73</v>
       </c>
     </row>
     <row r="382">
@@ -23757,7 +23757,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>13772.8</v>
+        <v>13869.19</v>
       </c>
     </row>
     <row r="383">
@@ -23818,7 +23818,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>5949.07</v>
+        <v>5990.7</v>
       </c>
     </row>
     <row r="384">
@@ -23879,7 +23879,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>4537.36</v>
+        <v>4569.11</v>
       </c>
     </row>
     <row r="385">
@@ -23940,7 +23940,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>1108.77</v>
+        <v>1116.53</v>
       </c>
     </row>
     <row r="386">
@@ -24001,7 +24001,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>2261.97</v>
+        <v>2277.8</v>
       </c>
     </row>
     <row r="387">
@@ -24062,7 +24062,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>17244.61</v>
+        <v>17365.3</v>
       </c>
     </row>
     <row r="388">
@@ -24123,7 +24123,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>9158.889999999999</v>
+        <v>9222.98</v>
       </c>
     </row>
     <row r="389">
@@ -24184,7 +24184,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>2700.71</v>
+        <v>2692.18</v>
       </c>
     </row>
     <row r="390">
@@ -24245,7 +24245,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>640.89</v>
+        <v>638.86</v>
       </c>
     </row>
     <row r="391">
@@ -24306,7 +24306,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>9415.9</v>
+        <v>9386.16</v>
       </c>
     </row>
     <row r="392">
@@ -24367,7 +24367,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>33041.4</v>
+        <v>32937.03</v>
       </c>
     </row>
     <row r="393">
@@ -24428,7 +24428,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>8183.93</v>
+        <v>8158.08</v>
       </c>
     </row>
     <row r="394">
@@ -24489,7 +24489,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>8310.02</v>
+        <v>8283.780000000001</v>
       </c>
     </row>
     <row r="395">
@@ -24550,7 +24550,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>695.29</v>
+        <v>693.09</v>
       </c>
     </row>
     <row r="396">
@@ -24611,7 +24611,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>52292.81</v>
+        <v>52127.63</v>
       </c>
     </row>
     <row r="397">
@@ -24672,7 +24672,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>352.19</v>
+        <v>351.08</v>
       </c>
     </row>
     <row r="398">
@@ -24733,7 +24733,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>8118.54</v>
+        <v>8092.9</v>
       </c>
     </row>
     <row r="399">
@@ -24794,7 +24794,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>4308.85</v>
+        <v>4295.24</v>
       </c>
     </row>
     <row r="400">
@@ -24855,7 +24855,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>632.77</v>
+        <v>630.77</v>
       </c>
     </row>
     <row r="401">
@@ -24916,7 +24916,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>35382.51</v>
+        <v>35270.75</v>
       </c>
     </row>
     <row r="402">
@@ -24977,7 +24977,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>2773.77</v>
+        <v>2765.01</v>
       </c>
     </row>
     <row r="403">
@@ -25038,7 +25038,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>4535.56</v>
+        <v>4521.23</v>
       </c>
     </row>
     <row r="404">
@@ -25099,7 +25099,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>7363.1</v>
+        <v>7339.85</v>
       </c>
     </row>
     <row r="405">
@@ -25160,7 +25160,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>10384.39</v>
+        <v>10351.59</v>
       </c>
     </row>
     <row r="406">
@@ -25221,7 +25221,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>16617.08</v>
+        <v>16564.59</v>
       </c>
     </row>
     <row r="407">
@@ -25282,7 +25282,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>3584.97</v>
+        <v>3573.65</v>
       </c>
     </row>
     <row r="408">
@@ -25343,7 +25343,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>22476.19</v>
+        <v>22405.2</v>
       </c>
     </row>
     <row r="409">
@@ -25404,7 +25404,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>3591.74</v>
+        <v>3580.4</v>
       </c>
     </row>
     <row r="410">
@@ -25465,7 +25465,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>3434.67</v>
+        <v>3423.82</v>
       </c>
     </row>
     <row r="411">
@@ -25526,7 +25526,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>42804.5</v>
+        <v>42669.29</v>
       </c>
     </row>
     <row r="412">
@@ -25587,7 +25587,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>890.22</v>
+        <v>887.41</v>
       </c>
     </row>
     <row r="413">
@@ -25648,7 +25648,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>1798.1</v>
+        <v>1792.42</v>
       </c>
     </row>
     <row r="414">
@@ -25709,7 +25709,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>1128.61</v>
+        <v>1125.04</v>
       </c>
     </row>
     <row r="415">
@@ -25770,7 +25770,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>6950.09</v>
+        <v>6928.14</v>
       </c>
     </row>
     <row r="416">
@@ -25831,7 +25831,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>1433.03</v>
+        <v>1428.5</v>
       </c>
     </row>
     <row r="417">
@@ -25892,7 +25892,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>4024.18</v>
+        <v>4011.47</v>
       </c>
     </row>
     <row r="418">
@@ -25953,7 +25953,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>1045.66</v>
+        <v>1042.36</v>
       </c>
     </row>
     <row r="419">
@@ -26014,7 +26014,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>702.77</v>
+        <v>700.55</v>
       </c>
     </row>
     <row r="420">
@@ -26075,7 +26075,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>5368.59</v>
+        <v>5351.64</v>
       </c>
     </row>
     <row r="421">
@@ -26136,7 +26136,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>3592.37</v>
+        <v>3581.02</v>
       </c>
     </row>
     <row r="422">
@@ -26197,7 +26197,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>18964.35</v>
+        <v>18904.45</v>
       </c>
     </row>
     <row r="423">
@@ -26258,7 +26258,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>12846.28</v>
+        <v>12805.7</v>
       </c>
     </row>
     <row r="424">
@@ -26319,7 +26319,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>1865.5</v>
+        <v>1859.6</v>
       </c>
     </row>
     <row r="425">
@@ -26380,7 +26380,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>2350.04</v>
+        <v>2342.61</v>
       </c>
     </row>
     <row r="426">
@@ -26441,7 +26441,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>651.89</v>
+        <v>649.83</v>
       </c>
     </row>
     <row r="427">
@@ -26502,7 +26502,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>373.1</v>
+        <v>371.92</v>
       </c>
     </row>
     <row r="428">
@@ -26563,7 +26563,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>39187.16</v>
+        <v>39063.38</v>
       </c>
     </row>
     <row r="429">
@@ -26624,7 +26624,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>10788.57</v>
+        <v>10754.5</v>
       </c>
     </row>
     <row r="430">
@@ -26685,7 +26685,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>32136.72</v>
+        <v>32035.21</v>
       </c>
     </row>
     <row r="431">
@@ -26746,7 +26746,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>3254.37</v>
+        <v>3244.09</v>
       </c>
     </row>
     <row r="432">
@@ -26807,7 +26807,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>3112.13</v>
+        <v>3102.3</v>
       </c>
     </row>
     <row r="433">
@@ -26868,7 +26868,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>12173.39</v>
+        <v>12134.94</v>
       </c>
     </row>
     <row r="434">
@@ -26929,7 +26929,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>646.26</v>
+        <v>644.22</v>
       </c>
     </row>
     <row r="435">
@@ -26990,7 +26990,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>8990.48</v>
+        <v>8962.08</v>
       </c>
     </row>
     <row r="436">
@@ -27051,7 +27051,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>665</v>
+        <v>662.9</v>
       </c>
     </row>
     <row r="437">
@@ -27112,7 +27112,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>50271.51</v>
+        <v>50112.72</v>
       </c>
     </row>
     <row r="438">
@@ -27173,7 +27173,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>8183.77</v>
+        <v>8157.92</v>
       </c>
     </row>
     <row r="439">
@@ -27234,7 +27234,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>24794.98</v>
+        <v>24716.66</v>
       </c>
     </row>
     <row r="440">
@@ -27295,7 +27295,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>1040.32</v>
+        <v>1037.03</v>
       </c>
     </row>
     <row r="441">
@@ -27356,7 +27356,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>17847.12</v>
+        <v>17790.75</v>
       </c>
     </row>
     <row r="442">
@@ -27417,7 +27417,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>3343.74</v>
+        <v>3333.18</v>
       </c>
     </row>
     <row r="443">
@@ -27478,7 +27478,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>59640.22</v>
+        <v>59451.84</v>
       </c>
     </row>
     <row r="444">
@@ -27539,7 +27539,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>672.66</v>
+        <v>671.2</v>
       </c>
     </row>
     <row r="445">
@@ -27600,7 +27600,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>682.7</v>
+        <v>681.21</v>
       </c>
     </row>
     <row r="446">
@@ -27661,7 +27661,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>18790.08</v>
+        <v>18749.2</v>
       </c>
     </row>
     <row r="447">
@@ -27722,7 +27722,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>5752.07</v>
+        <v>5739.55</v>
       </c>
     </row>
     <row r="448">
@@ -27783,7 +27783,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>14316.03</v>
+        <v>14284.88</v>
       </c>
     </row>
     <row r="449">
@@ -27844,7 +27844,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>1157.36</v>
+        <v>1154.84</v>
       </c>
     </row>
     <row r="450">
@@ -27905,7 +27905,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>5907.49</v>
+        <v>5894.64</v>
       </c>
     </row>
     <row r="451">
@@ -27966,7 +27966,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>277.87</v>
+        <v>277.26</v>
       </c>
     </row>
     <row r="452">
@@ -28027,7 +28027,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>48515.65</v>
+        <v>48410.09</v>
       </c>
     </row>
     <row r="453">
@@ -28088,7 +28088,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>2330.88</v>
+        <v>2325.81</v>
       </c>
     </row>
     <row r="454">
@@ -28149,7 +28149,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>5962.97</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="455">
@@ -28210,7 +28210,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>2544.94</v>
+        <v>2539.41</v>
       </c>
     </row>
     <row r="456">
@@ -28271,7 +28271,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>53011.67</v>
+        <v>52896.33</v>
       </c>
     </row>
     <row r="457">
@@ -28332,7 +28332,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>2160.6</v>
+        <v>2155.9</v>
       </c>
     </row>
     <row r="458">
@@ -28393,7 +28393,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>1117.5</v>
+        <v>1115.07</v>
       </c>
     </row>
     <row r="459">
@@ -28454,7 +28454,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>34072.17</v>
+        <v>33998.03</v>
       </c>
     </row>
     <row r="460">
@@ -28515,7 +28515,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>8112.58</v>
+        <v>8094.93</v>
       </c>
     </row>
     <row r="461">
@@ -28576,7 +28576,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>3240.91</v>
+        <v>3233.85</v>
       </c>
     </row>
     <row r="462">
@@ -28637,7 +28637,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>60658.08</v>
+        <v>60526.1</v>
       </c>
     </row>
     <row r="463">
@@ -28698,7 +28698,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>1652.8</v>
+        <v>1649.2</v>
       </c>
     </row>
     <row r="464">
@@ -28759,7 +28759,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>16931.11</v>
+        <v>16894.28</v>
       </c>
     </row>
     <row r="465">
@@ -28820,7 +28820,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>3247.64</v>
+        <v>3240.58</v>
       </c>
     </row>
     <row r="466">
@@ -28881,7 +28881,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>1623.19</v>
+        <v>1619.66</v>
       </c>
     </row>
     <row r="467">
@@ -28942,7 +28942,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>3787.13</v>
+        <v>3778.89</v>
       </c>
     </row>
     <row r="468">
@@ -29003,7 +29003,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>651.9</v>
+        <v>650.48</v>
       </c>
     </row>
     <row r="469">
@@ -29064,7 +29064,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>10803.02</v>
+        <v>10779.51</v>
       </c>
     </row>
     <row r="470">
@@ -29125,7 +29125,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>5401.51</v>
+        <v>5389.76</v>
       </c>
     </row>
     <row r="471">
@@ -29186,7 +29186,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>17936.01</v>
+        <v>17896.99</v>
       </c>
     </row>
     <row r="472">
@@ -29247,7 +29247,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>9535.18</v>
+        <v>9514.43</v>
       </c>
     </row>
     <row r="473">
@@ -29308,7 +29308,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>1058.07</v>
+        <v>1055.77</v>
       </c>
     </row>
     <row r="474">
@@ -29369,7 +29369,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>118083.12</v>
+        <v>117826.2</v>
       </c>
     </row>
     <row r="475">
@@ -29430,7 +29430,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>6135.54</v>
+        <v>6122.19</v>
       </c>
     </row>
     <row r="476">
@@ -29491,7 +29491,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>1058.06</v>
+        <v>1055.76</v>
       </c>
     </row>
     <row r="477">
@@ -29552,7 +29552,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>395892.6</v>
+        <v>395031.23</v>
       </c>
     </row>
     <row r="478">
@@ -29613,7 +29613,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>182838.46</v>
+        <v>182440.65</v>
       </c>
     </row>
     <row r="479">
@@ -29674,7 +29674,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>34399.05</v>
+        <v>34324.21</v>
       </c>
     </row>
     <row r="480">
@@ -29735,7 +29735,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>103797.06</v>
+        <v>103571.22</v>
       </c>
     </row>
     <row r="481">
@@ -29796,7 +29796,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>81137.64</v>
+        <v>80961.10000000001</v>
       </c>
     </row>
     <row r="482">
@@ -29857,7 +29857,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>120292.59</v>
+        <v>120030.86</v>
       </c>
     </row>
     <row r="483">
@@ -29918,7 +29918,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>309352.45</v>
+        <v>308679.37</v>
       </c>
     </row>
     <row r="484">
@@ -29979,7 +29979,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>39706.44</v>
+        <v>39620.04</v>
       </c>
     </row>
     <row r="485">
@@ -30040,7 +30040,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>152521.89</v>
+        <v>152190.04</v>
       </c>
     </row>
     <row r="486">
@@ -30101,7 +30101,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>7731.95</v>
+        <v>7715.12</v>
       </c>
     </row>
     <row r="487">
@@ -30162,7 +30162,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>19431.37</v>
+        <v>19389.09</v>
       </c>
     </row>
     <row r="488">
@@ -30223,7 +30223,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>36882.11</v>
+        <v>36801.87</v>
       </c>
     </row>
     <row r="489">
@@ -30284,7 +30284,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>25838.28</v>
+        <v>25782.06</v>
       </c>
     </row>
     <row r="490">
@@ -30345,7 +30345,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>5868.07</v>
+        <v>5855.3</v>
       </c>
     </row>
     <row r="491">
@@ -30406,7 +30406,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>75616.64999999999</v>
+        <v>75452.12</v>
       </c>
     </row>
     <row r="492">
@@ -30467,7 +30467,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>21254.3</v>
+        <v>21208.06</v>
       </c>
     </row>
     <row r="493">
@@ -30528,7 +30528,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>55007</v>
+        <v>54887.32</v>
       </c>
     </row>
     <row r="494">
@@ -30589,7 +30589,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>4647.54</v>
+        <v>4637.43</v>
       </c>
     </row>
     <row r="495">
@@ -30650,7 +30650,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>1259.15</v>
+        <v>1256.41</v>
       </c>
     </row>
     <row r="496">
@@ -30711,7 +30711,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>4840.3</v>
+        <v>4829.77</v>
       </c>
     </row>
     <row r="497">
@@ -30772,7 +30772,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>12782.37</v>
+        <v>12754.56</v>
       </c>
     </row>
     <row r="498">
@@ -30833,7 +30833,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>108187.12</v>
+        <v>107970.24</v>
       </c>
     </row>
     <row r="499">
@@ -30894,7 +30894,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>111073.65</v>
+        <v>110850.99</v>
       </c>
     </row>
     <row r="500">
@@ -30955,7 +30955,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>18389</v>
+        <v>18352.13</v>
       </c>
     </row>
     <row r="501">
@@ -31016,7 +31016,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>81864.67</v>
+        <v>81700.56</v>
       </c>
     </row>
     <row r="502">
@@ -31077,7 +31077,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>2667.97</v>
+        <v>2662.62</v>
       </c>
     </row>
     <row r="503">
@@ -31138,7 +31138,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>28878.7</v>
+        <v>28820.81</v>
       </c>
     </row>
     <row r="504">
@@ -31199,7 +31199,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>62273.93</v>
+        <v>62149.1</v>
       </c>
     </row>
     <row r="505">
@@ -31260,7 +31260,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>185584.63</v>
+        <v>185212.6</v>
       </c>
     </row>
     <row r="506">
@@ -31321,7 +31321,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>9365.059999999999</v>
+        <v>9346.290000000001</v>
       </c>
     </row>
     <row r="507">
@@ -31382,7 +31382,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>261000.59</v>
+        <v>260477.38</v>
       </c>
     </row>
     <row r="508">
@@ -31443,7 +31443,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>264482.64</v>
+        <v>263952.45</v>
       </c>
     </row>
     <row r="509">
@@ -31504,7 +31504,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>3821.42</v>
+        <v>3813.76</v>
       </c>
     </row>
     <row r="510">
@@ -31565,7 +31565,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>2147.44</v>
+        <v>2143.13</v>
       </c>
     </row>
     <row r="511">
@@ -31626,7 +31626,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>5382.4</v>
+        <v>5371.61</v>
       </c>
     </row>
     <row r="512">
@@ -31687,7 +31687,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>3442.36</v>
+        <v>3435.45</v>
       </c>
     </row>
     <row r="513">
@@ -31748,7 +31748,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>61834.7</v>
+        <v>61710.74</v>
       </c>
     </row>
     <row r="514">
@@ -31809,7 +31809,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>489.17</v>
+        <v>488.19</v>
       </c>
     </row>
     <row r="515">
@@ -31870,7 +31870,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>2288.52</v>
+        <v>2283.93</v>
       </c>
     </row>
     <row r="516">
@@ -31931,7 +31931,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>4722.57</v>
+        <v>4713.11</v>
       </c>
     </row>
     <row r="517">
@@ -31992,7 +31992,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>10925.09</v>
+        <v>10903.19</v>
       </c>
     </row>
     <row r="518">
@@ -32053,7 +32053,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>212514.44</v>
+        <v>212088.43</v>
       </c>
     </row>
     <row r="519">
@@ -32114,7 +32114,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>11080.68</v>
+        <v>11016.54</v>
       </c>
     </row>
     <row r="520">
@@ -32175,7 +32175,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>8629.18</v>
+        <v>8579.24</v>
       </c>
     </row>
     <row r="521">
@@ -32236,7 +32236,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>4300.23</v>
+        <v>4275.34</v>
       </c>
     </row>
     <row r="522">
@@ -32297,7 +32297,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>1165.43</v>
+        <v>1158.69</v>
       </c>
     </row>
     <row r="523">
@@ -32358,7 +32358,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>31486.3</v>
+        <v>31304.05</v>
       </c>
     </row>
     <row r="524">
@@ -32419,7 +32419,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>5160.94</v>
+        <v>5131.07</v>
       </c>
     </row>
     <row r="525">
@@ -32480,7 +32480,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>1526.02</v>
+        <v>1517.19</v>
       </c>
     </row>
     <row r="526">
@@ -32541,7 +32541,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>1369.18</v>
+        <v>1361.25</v>
       </c>
     </row>
     <row r="527">
@@ -32602,7 +32602,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>14366.97</v>
+        <v>14283.81</v>
       </c>
     </row>
     <row r="528">
@@ -32663,7 +32663,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>9499.6</v>
+        <v>9444.610000000001</v>
       </c>
     </row>
     <row r="529">
@@ -32724,7 +32724,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>27778.65</v>
+        <v>27617.86</v>
       </c>
     </row>
     <row r="530">
@@ -32785,7 +32785,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>951.22</v>
+        <v>945.71</v>
       </c>
     </row>
     <row r="531">
@@ -32846,7 +32846,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>10167.04</v>
+        <v>10108.19</v>
       </c>
     </row>
     <row r="532">
@@ -32907,7 +32907,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>9234.540000000001</v>
+        <v>9181.09</v>
       </c>
     </row>
     <row r="533">
@@ -32968,7 +32968,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>1548.28</v>
+        <v>1539.32</v>
       </c>
     </row>
     <row r="534">
@@ -33029,7 +33029,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>635.21</v>
+        <v>631.53</v>
       </c>
     </row>
     <row r="535">
@@ -33090,7 +33090,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>8310.02</v>
+        <v>8261.93</v>
       </c>
     </row>
     <row r="536">
@@ -33151,7 +33151,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>8052.89</v>
+        <v>8006.28</v>
       </c>
     </row>
     <row r="537">
@@ -33212,7 +33212,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>30930.77</v>
+        <v>30751.74</v>
       </c>
     </row>
     <row r="538">
@@ -33273,7 +33273,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>121258.64</v>
+        <v>120556.78</v>
       </c>
     </row>
     <row r="539">
@@ -33334,7 +33334,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>116935.97</v>
+        <v>116259.12</v>
       </c>
     </row>
     <row r="540">
@@ -33395,7 +33395,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>60842.79</v>
+        <v>60490.62</v>
       </c>
     </row>
     <row r="541">
@@ -33456,7 +33456,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>11205.07</v>
+        <v>11140.21</v>
       </c>
     </row>
     <row r="542">
@@ -33517,7 +33517,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>230263.92</v>
+        <v>228931.11</v>
       </c>
     </row>
     <row r="543">
@@ -33578,7 +33578,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>34516.74</v>
+        <v>34316.95</v>
       </c>
     </row>
     <row r="544">
@@ -33639,7 +33639,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>54063.66</v>
+        <v>53750.73</v>
       </c>
     </row>
     <row r="545">
@@ -33700,7 +33700,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>29055.2</v>
+        <v>28887.02</v>
       </c>
     </row>
     <row r="546">
@@ -33761,7 +33761,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>5542.37</v>
+        <v>5510.29</v>
       </c>
     </row>
     <row r="547">
@@ -33822,7 +33822,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>7064.56</v>
+        <v>7023.67</v>
       </c>
     </row>
     <row r="548">
@@ -33883,7 +33883,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>26118.21</v>
+        <v>25967.03</v>
       </c>
     </row>
     <row r="549">
@@ -33944,7 +33944,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>10296.2</v>
+        <v>10236.6</v>
       </c>
     </row>
     <row r="550">
@@ -34005,7 +34005,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>506.52</v>
+        <v>503.58</v>
       </c>
     </row>
     <row r="551">
@@ -34066,7 +34066,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>37787.23</v>
+        <v>37568.51</v>
       </c>
     </row>
     <row r="552">
@@ -34127,7 +34127,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>10812.73</v>
+        <v>10750.15</v>
       </c>
     </row>
     <row r="553">
@@ -34188,7 +34188,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>2121.89</v>
+        <v>2109.61</v>
       </c>
     </row>
     <row r="554">
@@ -34249,7 +34249,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>2764.33</v>
+        <v>2748.33</v>
       </c>
     </row>
     <row r="555">
@@ -34310,7 +34310,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>8117.69</v>
+        <v>8070.7</v>
       </c>
     </row>
     <row r="556">
@@ -34371,7 +34371,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>2475.57</v>
+        <v>2461.24</v>
       </c>
     </row>
     <row r="557">
@@ -34432,7 +34432,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>541.1900000000001</v>
+        <v>538.0599999999999</v>
       </c>
     </row>
     <row r="558">
@@ -34493,7 +34493,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>21660.04</v>
+        <v>21534.67</v>
       </c>
     </row>
     <row r="559">
@@ -34554,7 +34554,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>7731.95</v>
+        <v>7687.19</v>
       </c>
     </row>
     <row r="560">
@@ -34615,7 +34615,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>440.38</v>
+        <v>437.83</v>
       </c>
     </row>
     <row r="561">
@@ -34676,7 +34676,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>35005.5</v>
+        <v>34802.88</v>
       </c>
     </row>
     <row r="562">
@@ -34737,7 +34737,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>2074.55</v>
+        <v>2062.54</v>
       </c>
     </row>
     <row r="563">
@@ -34798,7 +34798,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>21651.54</v>
+        <v>21526.22</v>
       </c>
     </row>
     <row r="564">
@@ -34859,7 +34859,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>9891.83</v>
+        <v>9834.57</v>
       </c>
     </row>
     <row r="565">
@@ -34920,7 +34920,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>1951.32</v>
+        <v>1940.02</v>
       </c>
     </row>
     <row r="566">
@@ -34981,7 +34981,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>2897.47</v>
+        <v>2880.7</v>
       </c>
     </row>
     <row r="567">
@@ -35042,7 +35042,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>70117.67</v>
+        <v>69711.82000000001</v>
       </c>
     </row>
     <row r="568">
@@ -35103,7 +35103,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>13928.93</v>
+        <v>13848.31</v>
       </c>
     </row>
     <row r="569">
@@ -35164,7 +35164,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>16016.8</v>
+        <v>15924.09</v>
       </c>
     </row>
     <row r="570">
@@ -35225,7 +35225,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>8629.18</v>
+        <v>8579.24</v>
       </c>
     </row>
     <row r="571">
@@ -35286,7 +35286,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>25615.86</v>
+        <v>25467.59</v>
       </c>
     </row>
     <row r="572">
@@ -35347,7 +35347,7 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>535543.52</v>
+        <v>532443.6899999999</v>
       </c>
     </row>
     <row r="573">
@@ -35408,7 +35408,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>1493.38</v>
+        <v>1484.74</v>
       </c>
     </row>
     <row r="574">
@@ -35469,7 +35469,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>8118.54</v>
+        <v>8071.55</v>
       </c>
     </row>
     <row r="575">
@@ -35530,7 +35530,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>1160.75</v>
+        <v>1154.03</v>
       </c>
     </row>
     <row r="576">
@@ -35591,7 +35591,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>16237.09</v>
+        <v>16143.1</v>
       </c>
     </row>
     <row r="577">
@@ -35652,7 +35652,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>39570.12</v>
+        <v>39341.08</v>
       </c>
     </row>
     <row r="578">
@@ -35713,7 +35713,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>47597.19</v>
+        <v>47321.69</v>
       </c>
     </row>
     <row r="579">
@@ -35774,7 +35774,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>5713.55</v>
+        <v>5680.47</v>
       </c>
     </row>
     <row r="580">
@@ -35835,7 +35835,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>7578.67</v>
+        <v>7534.8</v>
       </c>
     </row>
     <row r="581">
@@ -35896,7 +35896,7 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>319559.17</v>
+        <v>317709.5</v>
       </c>
     </row>
     <row r="582">
@@ -35957,7 +35957,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>49630.48</v>
+        <v>49343.21</v>
       </c>
     </row>
     <row r="583">
@@ -36018,7 +36018,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>175566.45</v>
+        <v>174550.24</v>
       </c>
     </row>
     <row r="584">
@@ -36079,7 +36079,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>62245.01</v>
+        <v>61240.53</v>
       </c>
     </row>
     <row r="585">
@@ -36140,7 +36140,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>664.35</v>
+        <v>653.62</v>
       </c>
     </row>
     <row r="586">
@@ -36201,7 +36201,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>1676.78</v>
+        <v>1649.72</v>
       </c>
     </row>
     <row r="587">
@@ -36262,7 +36262,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>2073.3</v>
+        <v>2039.84</v>
       </c>
     </row>
     <row r="588">
@@ -36323,7 +36323,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>22716.06</v>
+        <v>22349.47</v>
       </c>
     </row>
     <row r="589">
@@ -36384,7 +36384,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>5560.84</v>
+        <v>5471.1</v>
       </c>
     </row>
     <row r="590">
@@ -36445,7 +36445,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>10161.33</v>
+        <v>9997.35</v>
       </c>
     </row>
     <row r="591">
@@ -36506,7 +36506,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>10480.9</v>
+        <v>10311.77</v>
       </c>
     </row>
     <row r="592">
@@ -36567,7 +36567,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>245594</v>
+        <v>241630.72</v>
       </c>
     </row>
     <row r="593">
@@ -36628,7 +36628,7 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>852.6900000000001</v>
+        <v>838.9299999999999</v>
       </c>
     </row>
     <row r="594">
@@ -36689,7 +36689,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>8878.620000000001</v>
+        <v>8735.34</v>
       </c>
     </row>
     <row r="595">
@@ -36750,7 +36750,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>260.76</v>
+        <v>256.55</v>
       </c>
     </row>
     <row r="596">
@@ -36811,7 +36811,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>100321.64</v>
+        <v>98702.69</v>
       </c>
     </row>
     <row r="597">
@@ -36872,7 +36872,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>500166.34</v>
+        <v>492094.88</v>
       </c>
     </row>
     <row r="598">
@@ -36933,7 +36933,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>13204.85</v>
+        <v>12991.76</v>
       </c>
     </row>
     <row r="599">
@@ -36994,7 +36994,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>37875.59</v>
+        <v>37264.37</v>
       </c>
     </row>
     <row r="600">
@@ -37055,7 +37055,7 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>30038.56</v>
+        <v>29553.81</v>
       </c>
     </row>
     <row r="601">
@@ -37116,7 +37116,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>8115.97</v>
+        <v>7985</v>
       </c>
     </row>
     <row r="602">
@@ -37177,7 +37177,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>9967.84</v>
+        <v>9806.98</v>
       </c>
     </row>
     <row r="603">
@@ -37238,7 +37238,7 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>1183.74</v>
+        <v>1164.64</v>
       </c>
     </row>
     <row r="604">
@@ -37299,7 +37299,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>142.84</v>
+        <v>140.54</v>
       </c>
     </row>
     <row r="605">
@@ -37360,7 +37360,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>586.67</v>
+        <v>577.2</v>
       </c>
     </row>
     <row r="606">
@@ -37421,7 +37421,7 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>92851.75</v>
+        <v>91353.35000000001</v>
       </c>
     </row>
     <row r="607">
@@ -37482,7 +37482,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>49829.53</v>
+        <v>49025.4</v>
       </c>
     </row>
     <row r="608">
@@ -37543,7 +37543,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>40366.65</v>
+        <v>39715.24</v>
       </c>
     </row>
     <row r="609">
@@ -37604,7 +37604,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>18503.88</v>
+        <v>18205.27</v>
       </c>
     </row>
     <row r="610">
@@ -37665,7 +37665,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>8310.719999999999</v>
+        <v>8176.61</v>
       </c>
     </row>
     <row r="611">
@@ -37726,7 +37726,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>675.9400000000001</v>
+        <v>665.03</v>
       </c>
     </row>
     <row r="612">
@@ -37787,7 +37787,7 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>915.2</v>
+        <v>900.4299999999999</v>
       </c>
     </row>
     <row r="613">
@@ -37848,7 +37848,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>29003.44</v>
+        <v>28535.4</v>
       </c>
     </row>
     <row r="614">
@@ -37909,7 +37909,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>486.75</v>
+        <v>478.9</v>
       </c>
     </row>
     <row r="615">
@@ -37970,7 +37970,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>5996.14</v>
+        <v>5899.38</v>
       </c>
     </row>
     <row r="616">
@@ -38031,7 +38031,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>5992.25</v>
+        <v>5895.55</v>
       </c>
     </row>
     <row r="617">
@@ -38092,7 +38092,7 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>5654.89</v>
+        <v>5563.63</v>
       </c>
     </row>
     <row r="618">
@@ -38153,7 +38153,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>7958.43</v>
+        <v>7830</v>
       </c>
     </row>
     <row r="619">
@@ -38214,7 +38214,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>12291.13</v>
+        <v>12092.78</v>
       </c>
     </row>
     <row r="620">
@@ -38275,7 +38275,7 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>9326.42</v>
+        <v>9175.92</v>
       </c>
     </row>
     <row r="621">
@@ -38336,7 +38336,7 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>159342.31</v>
+        <v>156770.91</v>
       </c>
     </row>
     <row r="622">
@@ -38397,7 +38397,7 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>37565.73</v>
+        <v>36959.51</v>
       </c>
     </row>
     <row r="623">
@@ -38458,7 +38458,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>1210.07</v>
+        <v>1190.55</v>
       </c>
     </row>
     <row r="624">
@@ -38519,7 +38519,7 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>1433.64</v>
+        <v>1410.51</v>
       </c>
     </row>
     <row r="625">
@@ -38580,7 +38580,7 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>4120.04</v>
+        <v>4053.55</v>
       </c>
     </row>
     <row r="626">
@@ -38641,7 +38641,7 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>8118.54</v>
+        <v>7987.53</v>
       </c>
     </row>
     <row r="627">
@@ -38702,7 +38702,7 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>481305.19</v>
+        <v>473538.1</v>
       </c>
     </row>
     <row r="628">
@@ -38763,7 +38763,7 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>231202.59</v>
+        <v>227471.55</v>
       </c>
     </row>
     <row r="629">
@@ -38824,7 +38824,7 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>3423.32</v>
+        <v>3368.08</v>
       </c>
     </row>
     <row r="630">
@@ -38885,7 +38885,7 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>29216.17</v>
+        <v>28744.69</v>
       </c>
     </row>
     <row r="631">
@@ -38946,7 +38946,7 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>10680.08</v>
+        <v>10507.73</v>
       </c>
     </row>
     <row r="632">
@@ -39007,7 +39007,7 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>4850.35</v>
+        <v>4772.07</v>
       </c>
     </row>
     <row r="633">
@@ -39068,7 +39068,7 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>185703.5</v>
+        <v>182706.7</v>
       </c>
     </row>
     <row r="634">
@@ -39129,7 +39129,7 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>35683.36</v>
+        <v>35107.52</v>
       </c>
     </row>
     <row r="635">
@@ -39190,7 +39190,7 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>24785.52</v>
+        <v>24385.54</v>
       </c>
     </row>
     <row r="636">
@@ -39251,7 +39251,7 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>20087.24</v>
+        <v>19763.08</v>
       </c>
     </row>
     <row r="637">
@@ -39312,7 +39312,7 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>1564.82</v>
+        <v>1539.57</v>
       </c>
     </row>
     <row r="638">
@@ -39373,7 +39373,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>1937.87</v>
+        <v>1906.6</v>
       </c>
     </row>
     <row r="639">
@@ -39434,7 +39434,7 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>6002.34</v>
+        <v>5905.48</v>
       </c>
     </row>
     <row r="640">
@@ -39495,7 +39495,7 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>185588.46</v>
+        <v>182593.52</v>
       </c>
     </row>
     <row r="641">
@@ -39556,7 +39556,7 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>18416.58</v>
+        <v>18121.29</v>
       </c>
     </row>
     <row r="642">
@@ -39617,7 +39617,7 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>442.83</v>
+        <v>435.73</v>
       </c>
     </row>
     <row r="643">
@@ -39678,7 +39678,7 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>829.77</v>
+        <v>816.46</v>
       </c>
     </row>
     <row r="644">
@@ -39739,7 +39739,7 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>8167.96</v>
+        <v>8037</v>
       </c>
     </row>
     <row r="645">
@@ -39800,7 +39800,7 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>1968.89</v>
+        <v>1937.33</v>
       </c>
     </row>
     <row r="646">
@@ -39861,7 +39861,7 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>848.51</v>
+        <v>834.91</v>
       </c>
     </row>
     <row r="647">
@@ -39922,7 +39922,7 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>19307.57</v>
+        <v>18998</v>
       </c>
     </row>
     <row r="648">
@@ -39983,7 +39983,7 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>1206.66</v>
+        <v>1187.31</v>
       </c>
     </row>
     <row r="649">
@@ -40044,7 +40044,7 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>261.01</v>
+        <v>256.83</v>
       </c>
     </row>
     <row r="650">
@@ -40105,7 +40105,7 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>6003.84</v>
+        <v>5907.57</v>
       </c>
     </row>
     <row r="651">
@@ -40166,7 +40166,7 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>441.28</v>
+        <v>434.2</v>
       </c>
     </row>
     <row r="652">
@@ -40227,7 +40227,7 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>472.82</v>
+        <v>465.24</v>
       </c>
     </row>
     <row r="653">
@@ -40288,7 +40288,7 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>7993.97</v>
+        <v>7865.8</v>
       </c>
     </row>
     <row r="654">
@@ -40349,7 +40349,7 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>277.51</v>
+        <v>273.06</v>
       </c>
     </row>
     <row r="655">
@@ -40410,7 +40410,7 @@
         </is>
       </c>
       <c r="M655" s="2" t="n">
-        <v>7731.13</v>
+        <v>7607.17</v>
       </c>
     </row>
     <row r="656">
@@ -40471,7 +40471,7 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>650.6900000000001</v>
+        <v>640.25</v>
       </c>
     </row>
     <row r="657">
@@ -40532,7 +40532,7 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>2433.76</v>
+        <v>2394.73</v>
       </c>
     </row>
     <row r="658">
@@ -40593,7 +40593,7 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>8117.68</v>
+        <v>7987.52</v>
       </c>
     </row>
     <row r="659">
@@ -40654,7 +40654,7 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>8113.98</v>
+        <v>7983.88</v>
       </c>
     </row>
     <row r="660">
@@ -40715,7 +40715,7 @@
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>712.39</v>
+        <v>700.97</v>
       </c>
     </row>
     <row r="661">
@@ -40776,7 +40776,7 @@
         </is>
       </c>
       <c r="M661" s="2" t="n">
-        <v>360.06</v>
+        <v>354.28</v>
       </c>
     </row>
     <row r="662">
@@ -40837,7 +40837,7 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>185891.4</v>
+        <v>182910.9</v>
       </c>
     </row>
     <row r="663">
@@ -40898,7 +40898,7 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>8310.02</v>
+        <v>8176.79</v>
       </c>
     </row>
     <row r="664">
@@ -40959,7 +40959,7 @@
         </is>
       </c>
       <c r="M664" s="2" t="n">
-        <v>529.91</v>
+        <v>521.41</v>
       </c>
     </row>
     <row r="665">
@@ -41020,7 +41020,7 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>8310.02</v>
+        <v>8176.79</v>
       </c>
     </row>
     <row r="666">
@@ -41081,7 +41081,7 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>89.56</v>
+        <v>88.13</v>
       </c>
     </row>
     <row r="667">
@@ -41142,7 +41142,7 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>20596.23</v>
+        <v>20266</v>
       </c>
     </row>
     <row r="668">
@@ -41203,7 +41203,7 @@
         </is>
       </c>
       <c r="M668" s="2" t="n">
-        <v>8310.719999999999</v>
+        <v>8177.47</v>
       </c>
     </row>
     <row r="669">
@@ -41264,7 +41264,7 @@
         </is>
       </c>
       <c r="M669" s="2" t="n">
-        <v>529.91</v>
+        <v>521.41</v>
       </c>
     </row>
     <row r="670">
@@ -41325,7 +41325,7 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>41</v>
+        <v>40.34</v>
       </c>
     </row>
     <row r="671">
@@ -41386,7 +41386,7 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>8310.719999999999</v>
+        <v>8177.47</v>
       </c>
     </row>
     <row r="672">
@@ -41447,7 +41447,7 @@
         </is>
       </c>
       <c r="M672" s="2" t="n">
-        <v>531.36</v>
+        <v>522.84</v>
       </c>
     </row>
     <row r="673">
@@ -41508,7 +41508,7 @@
         </is>
       </c>
       <c r="M673" s="2" t="n">
-        <v>69913.81</v>
+        <v>68792.84</v>
       </c>
     </row>
     <row r="674">
@@ -41569,7 +41569,7 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>187.71</v>
+        <v>184.7</v>
       </c>
     </row>
     <row r="675">
@@ -41630,7 +41630,7 @@
         </is>
       </c>
       <c r="M675" s="2" t="n">
-        <v>2866.21</v>
+        <v>2820.25</v>
       </c>
     </row>
     <row r="676">
@@ -41691,7 +41691,7 @@
         </is>
       </c>
       <c r="M676" s="2" t="n">
-        <v>670.47</v>
+        <v>659.72</v>
       </c>
     </row>
     <row r="677">
@@ -41752,7 +41752,7 @@
         </is>
       </c>
       <c r="M677" s="2" t="n">
-        <v>531.36</v>
+        <v>522.84</v>
       </c>
     </row>
     <row r="678">
@@ -41813,7 +41813,7 @@
         </is>
       </c>
       <c r="M678" s="2" t="n">
-        <v>8167.96</v>
+        <v>8072.92</v>
       </c>
     </row>
     <row r="679">
@@ -41874,7 +41874,7 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>569.4</v>
+        <v>562.78</v>
       </c>
     </row>
     <row r="680">
@@ -41935,7 +41935,7 @@
         </is>
       </c>
       <c r="M680" s="2" t="n">
-        <v>30930.77</v>
+        <v>30570.87</v>
       </c>
     </row>
     <row r="681">
@@ -41996,7 +41996,7 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>8117.69</v>
+        <v>8023.23</v>
       </c>
     </row>
     <row r="682">
@@ -42057,7 +42057,7 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>1239.08</v>
+        <v>1224.66</v>
       </c>
     </row>
     <row r="683">
@@ -42118,7 +42118,7 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>8878.620000000001</v>
+        <v>8775.309999999999</v>
       </c>
     </row>
     <row r="684">
@@ -42179,7 +42179,7 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>445.57</v>
+        <v>440.38</v>
       </c>
     </row>
     <row r="685">
@@ -42240,7 +42240,7 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>2914.71</v>
+        <v>2880.79</v>
       </c>
     </row>
     <row r="686">
@@ -42301,7 +42301,7 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>640.4299999999999</v>
+        <v>632.98</v>
       </c>
     </row>
     <row r="687">
@@ -42362,7 +42362,7 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>7759.58</v>
+        <v>7669.29</v>
       </c>
     </row>
     <row r="688">
@@ -42423,7 +42423,7 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>25553.51</v>
+        <v>25256.18</v>
       </c>
     </row>
     <row r="689">
@@ -42484,7 +42484,7 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>3886.27</v>
+        <v>3841.05</v>
       </c>
     </row>
     <row r="690">
@@ -42545,7 +42545,7 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>1352.21</v>
+        <v>1336.48</v>
       </c>
     </row>
     <row r="691">
@@ -42606,7 +42606,7 @@
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>8014.08</v>
+        <v>7920.83</v>
       </c>
     </row>
     <row r="692">
@@ -42667,7 +42667,7 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>7731.95</v>
+        <v>7641.98</v>
       </c>
     </row>
     <row r="693">
@@ -42728,7 +42728,7 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>239.88</v>
+        <v>237.08</v>
       </c>
     </row>
     <row r="694">
@@ -42789,7 +42789,7 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>7731.95</v>
+        <v>7641.98</v>
       </c>
     </row>
     <row r="695">
@@ -42850,7 +42850,7 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>682.59</v>
+        <v>674.65</v>
       </c>
     </row>
     <row r="696">
@@ -42911,7 +42911,7 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>7772.6</v>
+        <v>7682.16</v>
       </c>
     </row>
     <row r="697">
@@ -42972,7 +42972,7 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>8183.77</v>
+        <v>8088.54</v>
       </c>
     </row>
     <row r="698">
@@ -43033,7 +43033,7 @@
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>134.77</v>
+        <v>133.21</v>
       </c>
     </row>
     <row r="699">
@@ -43094,7 +43094,7 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>891.14</v>
+        <v>880.77</v>
       </c>
     </row>
     <row r="700">
@@ -43155,7 +43155,7 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>2185.66</v>
+        <v>2160.23</v>
       </c>
     </row>
     <row r="701">
@@ -43216,7 +43216,7 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>16367.53</v>
+        <v>16177.09</v>
       </c>
     </row>
     <row r="702">
@@ -43277,7 +43277,7 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>17757.24</v>
+        <v>17550.62</v>
       </c>
     </row>
     <row r="703">
@@ -43338,7 +43338,7 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>2812.34</v>
+        <v>2779.61</v>
       </c>
     </row>
     <row r="704">
@@ -43399,7 +43399,7 @@
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>5303.56</v>
+        <v>5241.85</v>
       </c>
     </row>
     <row r="705">
@@ -43460,7 +43460,7 @@
         </is>
       </c>
       <c r="M705" s="2" t="n">
-        <v>2535.97</v>
+        <v>2506.46</v>
       </c>
     </row>
     <row r="706">
@@ -43521,7 +43521,7 @@
         </is>
       </c>
       <c r="M706" s="2" t="n">
-        <v>4041.56</v>
+        <v>3994.54</v>
       </c>
     </row>
     <row r="707">
@@ -43582,7 +43582,7 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>9011.57</v>
+        <v>8906.709999999999</v>
       </c>
     </row>
     <row r="708">
@@ -43643,7 +43643,7 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>3459.92</v>
+        <v>3419.66</v>
       </c>
     </row>
     <row r="709">
@@ -43704,7 +43704,7 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>1240.3</v>
+        <v>1225.87</v>
       </c>
     </row>
     <row r="710">
@@ -43765,7 +43765,7 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>345.15</v>
+        <v>341.13</v>
       </c>
     </row>
     <row r="711">
@@ -43826,7 +43826,7 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>1299.6</v>
+        <v>1284.48</v>
       </c>
     </row>
     <row r="712">
@@ -43887,7 +43887,7 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>252.27</v>
+        <v>249.34</v>
       </c>
     </row>
     <row r="713">
@@ -43948,7 +43948,7 @@
         </is>
       </c>
       <c r="M713" s="2" t="n">
-        <v>167.42</v>
+        <v>165.48</v>
       </c>
     </row>
     <row r="714">
@@ -44009,7 +44009,7 @@
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>261.01</v>
+        <v>257.98</v>
       </c>
     </row>
     <row r="715">
@@ -44070,7 +44070,7 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>40932.33</v>
+        <v>40456.06</v>
       </c>
     </row>
     <row r="716">
@@ -44131,7 +44131,7 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>451.73</v>
+        <v>446.48</v>
       </c>
     </row>
     <row r="717">
@@ -44192,7 +44192,7 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>16310.3</v>
+        <v>16120.52</v>
       </c>
     </row>
     <row r="718">
@@ -44253,7 +44253,7 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>24551.3</v>
+        <v>24265.63</v>
       </c>
     </row>
     <row r="719">
@@ -44314,7 +44314,7 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>2110.11</v>
+        <v>2085.56</v>
       </c>
     </row>
     <row r="720">
@@ -44375,7 +44375,7 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>733.08</v>
+        <v>724.55</v>
       </c>
     </row>
     <row r="721">
@@ -44436,7 +44436,7 @@
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>18278.18</v>
+        <v>18065.5</v>
       </c>
     </row>
     <row r="722">
@@ -44497,7 +44497,7 @@
         </is>
       </c>
       <c r="M722" s="2" t="n">
-        <v>488.67</v>
+        <v>485.96</v>
       </c>
     </row>
     <row r="723">
@@ -44558,7 +44558,7 @@
         </is>
       </c>
       <c r="M723" s="2" t="n">
-        <v>46597.59</v>
+        <v>46339.26</v>
       </c>
     </row>
     <row r="724">
@@ -44619,7 +44619,7 @@
         </is>
       </c>
       <c r="M724" s="2" t="n">
-        <v>8118.54</v>
+        <v>8073.54</v>
       </c>
     </row>
     <row r="725">
@@ -44680,7 +44680,7 @@
         </is>
       </c>
       <c r="M725" s="2" t="n">
-        <v>28913.55</v>
+        <v>28753.25</v>
       </c>
     </row>
     <row r="726">
@@ -44741,7 +44741,7 @@
         </is>
       </c>
       <c r="M726" s="2" t="n">
-        <v>8118.54</v>
+        <v>8073.54</v>
       </c>
     </row>
     <row r="727">
@@ -44802,7 +44802,7 @@
         </is>
       </c>
       <c r="M727" s="2" t="n">
-        <v>445.01</v>
+        <v>442.55</v>
       </c>
     </row>
     <row r="728">
@@ -44863,7 +44863,7 @@
         </is>
       </c>
       <c r="M728" s="2" t="n">
-        <v>8878.620000000001</v>
+        <v>8829.4</v>
       </c>
     </row>
     <row r="729">
@@ -44924,7 +44924,7 @@
         </is>
       </c>
       <c r="M729" s="2" t="n">
-        <v>62480.21</v>
+        <v>62133.82</v>
       </c>
     </row>
     <row r="730">
@@ -44985,7 +44985,7 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>7654.7</v>
+        <v>7612.26</v>
       </c>
     </row>
     <row r="731">
@@ -45046,7 +45046,7 @@
         </is>
       </c>
       <c r="M731" s="2" t="n">
-        <v>61901.17</v>
+        <v>61557.99</v>
       </c>
     </row>
     <row r="732">
@@ -45107,7 +45107,7 @@
         </is>
       </c>
       <c r="M732" s="2" t="n">
-        <v>695.5599999999999</v>
+        <v>691.71</v>
       </c>
     </row>
     <row r="733">
@@ -45168,7 +45168,7 @@
         </is>
       </c>
       <c r="M733" s="2" t="n">
-        <v>8586.870000000001</v>
+        <v>8539.27</v>
       </c>
     </row>
     <row r="734">
@@ -45229,7 +45229,7 @@
         </is>
       </c>
       <c r="M734" s="2" t="n">
-        <v>1730.92</v>
+        <v>1721.32</v>
       </c>
     </row>
     <row r="735">
@@ -45290,7 +45290,7 @@
         </is>
       </c>
       <c r="M735" s="2" t="n">
-        <v>4932.08</v>
+        <v>4904.73</v>
       </c>
     </row>
     <row r="736">
@@ -45351,7 +45351,7 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>30689.18</v>
+        <v>30519.05</v>
       </c>
     </row>
     <row r="737">
@@ -45412,7 +45412,7 @@
         </is>
       </c>
       <c r="M737" s="2" t="n">
-        <v>8878.620000000001</v>
+        <v>8829.4</v>
       </c>
     </row>
     <row r="738">
@@ -45473,7 +45473,7 @@
         </is>
       </c>
       <c r="M738" s="2" t="n">
-        <v>829.01</v>
+        <v>824.41</v>
       </c>
     </row>
     <row r="739">
@@ -45534,7 +45534,7 @@
         </is>
       </c>
       <c r="M739" s="2" t="n">
-        <v>32515.53</v>
+        <v>32335.27</v>
       </c>
     </row>
     <row r="740">
@@ -45595,7 +45595,7 @@
         </is>
       </c>
       <c r="M740" s="2" t="n">
-        <v>8117.68</v>
+        <v>8072.67</v>
       </c>
     </row>
     <row r="741">
@@ -45656,7 +45656,7 @@
         </is>
       </c>
       <c r="M741" s="2" t="n">
-        <v>958.64</v>
+        <v>953.3200000000001</v>
       </c>
     </row>
     <row r="742">
@@ -45717,7 +45717,7 @@
         </is>
       </c>
       <c r="M742" s="2" t="n">
-        <v>61861.54</v>
+        <v>61518.59</v>
       </c>
     </row>
     <row r="743">
@@ -45778,7 +45778,7 @@
         </is>
       </c>
       <c r="M743" s="2" t="n">
-        <v>591.1799999999999</v>
+        <v>587.9</v>
       </c>
     </row>
     <row r="744">
@@ -45839,7 +45839,7 @@
         </is>
       </c>
       <c r="M744" s="2" t="n">
-        <v>8183.93</v>
+        <v>8138.56</v>
       </c>
     </row>
     <row r="745">
@@ -45900,7 +45900,7 @@
         </is>
       </c>
       <c r="M745" s="2" t="n">
-        <v>7388.55</v>
+        <v>7347.59</v>
       </c>
     </row>
     <row r="746">
@@ -45961,7 +45961,7 @@
         </is>
       </c>
       <c r="M746" s="2" t="n">
-        <v>8118.54</v>
+        <v>8073.54</v>
       </c>
     </row>
     <row r="747">
@@ -46022,7 +46022,7 @@
         </is>
       </c>
       <c r="M747" s="2" t="n">
-        <v>17949.15</v>
+        <v>17849.64</v>
       </c>
     </row>
     <row r="748">
@@ -46083,7 +46083,7 @@
         </is>
       </c>
       <c r="M748" s="2" t="n">
-        <v>3893.3</v>
+        <v>3871.71</v>
       </c>
     </row>
     <row r="749">
@@ -46144,7 +46144,7 @@
         </is>
       </c>
       <c r="M749" s="2" t="n">
-        <v>16227.96</v>
+        <v>16137.99</v>
       </c>
     </row>
     <row r="750">
@@ -46205,7 +46205,7 @@
         </is>
       </c>
       <c r="M750" s="2" t="n">
-        <v>3415.69</v>
+        <v>3396.75</v>
       </c>
     </row>
     <row r="751">
@@ -46266,7 +46266,7 @@
         </is>
       </c>
       <c r="M751" s="2" t="n">
-        <v>3597.72</v>
+        <v>3577.78</v>
       </c>
     </row>
     <row r="752">
@@ -46327,7 +46327,7 @@
         </is>
       </c>
       <c r="M752" s="2" t="n">
-        <v>821.27</v>
+        <v>816.71</v>
       </c>
     </row>
     <row r="753">
@@ -46388,7 +46388,7 @@
         </is>
       </c>
       <c r="M753" s="2" t="n">
-        <v>20451.79</v>
+        <v>20338.4</v>
       </c>
     </row>
     <row r="754">
@@ -46449,7 +46449,7 @@
         </is>
       </c>
       <c r="M754" s="2" t="n">
-        <v>1389.82</v>
+        <v>1382.12</v>
       </c>
     </row>
     <row r="755">
@@ -46510,7 +46510,7 @@
         </is>
       </c>
       <c r="M755" s="2" t="n">
-        <v>996.08</v>
+        <v>990.5599999999999</v>
       </c>
     </row>
     <row r="756">
@@ -46571,7 +46571,7 @@
         </is>
       </c>
       <c r="M756" s="2" t="n">
-        <v>455.21</v>
+        <v>452.68</v>
       </c>
     </row>
     <row r="757">
@@ -46632,7 +46632,7 @@
         </is>
       </c>
       <c r="M757" s="2" t="n">
-        <v>8310.719999999999</v>
+        <v>8264.65</v>
       </c>
     </row>
     <row r="758">
@@ -46693,7 +46693,7 @@
         </is>
       </c>
       <c r="M758" s="2" t="n">
-        <v>73511.63</v>
+        <v>73104.09</v>
       </c>
     </row>
     <row r="759">
@@ -46754,7 +46754,7 @@
         </is>
       </c>
       <c r="M759" s="2" t="n">
-        <v>8878.620000000001</v>
+        <v>8829.4</v>
       </c>
     </row>
     <row r="760">
@@ -46815,7 +46815,7 @@
         </is>
       </c>
       <c r="M760" s="2" t="n">
-        <v>1620.07</v>
+        <v>1611.09</v>
       </c>
     </row>
     <row r="761">
@@ -46876,7 +46876,7 @@
         </is>
       </c>
       <c r="M761" s="2" t="n">
-        <v>886.61</v>
+        <v>881.6900000000001</v>
       </c>
     </row>
     <row r="762">
@@ -46937,7 +46937,7 @@
         </is>
       </c>
       <c r="M762" s="2" t="n">
-        <v>763.13</v>
+        <v>758.89</v>
       </c>
     </row>
     <row r="763">
@@ -46998,7 +46998,7 @@
         </is>
       </c>
       <c r="M763" s="2" t="n">
-        <v>3007.56</v>
+        <v>2990.89</v>
       </c>
     </row>
     <row r="764">
@@ -47059,7 +47059,7 @@
         </is>
       </c>
       <c r="M764" s="2" t="n">
-        <v>514.53</v>
+        <v>511.67</v>
       </c>
     </row>
     <row r="765">
@@ -47120,7 +47120,7 @@
         </is>
       </c>
       <c r="M765" s="2" t="n">
-        <v>5112.69</v>
+        <v>5084.35</v>
       </c>
     </row>
     <row r="766">
@@ -47181,7 +47181,7 @@
         </is>
       </c>
       <c r="M766" s="2" t="n">
-        <v>370.28</v>
+        <v>368.46</v>
       </c>
     </row>
     <row r="767">
@@ -47242,7 +47242,7 @@
         </is>
       </c>
       <c r="M767" s="2" t="n">
-        <v>16335.92</v>
+        <v>16255.6</v>
       </c>
     </row>
     <row r="768">
@@ -47303,7 +47303,7 @@
         </is>
       </c>
       <c r="M768" s="2" t="n">
-        <v>48103.74</v>
+        <v>47867.22</v>
       </c>
     </row>
     <row r="769">
@@ -47364,7 +47364,7 @@
         </is>
       </c>
       <c r="M769" s="2" t="n">
-        <v>8789.459999999999</v>
+        <v>8746.25</v>
       </c>
     </row>
     <row r="770">
@@ -47425,7 +47425,7 @@
         </is>
       </c>
       <c r="M770" s="2" t="n">
-        <v>2803.14</v>
+        <v>2789.36</v>
       </c>
     </row>
     <row r="771">
@@ -47486,7 +47486,7 @@
         </is>
       </c>
       <c r="M771" s="2" t="n">
-        <v>5757.05</v>
+        <v>5728.74</v>
       </c>
     </row>
     <row r="772">
@@ -47547,7 +47547,7 @@
         </is>
       </c>
       <c r="M772" s="2" t="n">
-        <v>108727.72</v>
+        <v>108193.13</v>
       </c>
     </row>
     <row r="773">
@@ -47608,7 +47608,7 @@
         </is>
       </c>
       <c r="M773" s="2" t="n">
-        <v>8310.02</v>
+        <v>8269.17</v>
       </c>
     </row>
     <row r="774">
@@ -47669,7 +47669,7 @@
         </is>
       </c>
       <c r="M774" s="2" t="n">
-        <v>545.17</v>
+        <v>542.49</v>
       </c>
     </row>
     <row r="775">
@@ -47730,7 +47730,7 @@
         </is>
       </c>
       <c r="M775" s="2" t="n">
-        <v>24851.22</v>
+        <v>24729.03</v>
       </c>
     </row>
     <row r="776">
@@ -47791,7 +47791,7 @@
         </is>
       </c>
       <c r="M776" s="2" t="n">
-        <v>1055.22</v>
+        <v>1050.03</v>
       </c>
     </row>
     <row r="777">
@@ -47852,7 +47852,7 @@
         </is>
       </c>
       <c r="M777" s="2" t="n">
-        <v>3067.77</v>
+        <v>3052.68</v>
       </c>
     </row>
     <row r="778">
@@ -47913,7 +47913,7 @@
         </is>
       </c>
       <c r="M778" s="2" t="n">
-        <v>1154.36</v>
+        <v>1148.68</v>
       </c>
     </row>
     <row r="779">
@@ -47974,7 +47974,7 @@
         </is>
       </c>
       <c r="M779" s="2" t="n">
-        <v>7132.16</v>
+        <v>7097.1</v>
       </c>
     </row>
     <row r="780">
@@ -48035,7 +48035,7 @@
         </is>
       </c>
       <c r="M780" s="2" t="n">
-        <v>1405.92</v>
+        <v>1399.01</v>
       </c>
     </row>
     <row r="781">
@@ -48096,7 +48096,7 @@
         </is>
       </c>
       <c r="M781" s="2" t="n">
-        <v>994.53</v>
+        <v>989.64</v>
       </c>
     </row>
     <row r="782">
@@ -48157,7 +48157,7 @@
         </is>
       </c>
       <c r="M782" s="2" t="n">
-        <v>776.02</v>
+        <v>772.2</v>
       </c>
     </row>
     <row r="783">
@@ -48218,7 +48218,7 @@
         </is>
       </c>
       <c r="M783" s="2" t="n">
-        <v>43138.15</v>
+        <v>42926.05</v>
       </c>
     </row>
     <row r="784">
@@ -48279,7 +48279,7 @@
         </is>
       </c>
       <c r="M784" s="2" t="n">
-        <v>8812.51</v>
+        <v>8769.18</v>
       </c>
     </row>
     <row r="785">
@@ -48340,7 +48340,7 @@
         </is>
       </c>
       <c r="M785" s="2" t="n">
-        <v>53093</v>
+        <v>52831.96</v>
       </c>
     </row>
     <row r="786">
@@ -48401,7 +48401,7 @@
         </is>
       </c>
       <c r="M786" s="2" t="n">
-        <v>92805.73</v>
+        <v>92349.42999999999</v>
       </c>
     </row>
     <row r="787">
@@ -48462,7 +48462,7 @@
         </is>
       </c>
       <c r="M787" s="2" t="n">
-        <v>2215.81</v>
+        <v>2204.91</v>
       </c>
     </row>
     <row r="788">
@@ -48523,7 +48523,7 @@
         </is>
       </c>
       <c r="M788" s="2" t="n">
-        <v>81864.67</v>
+        <v>81462.16</v>
       </c>
     </row>
     <row r="789">
@@ -48584,7 +48584,7 @@
         </is>
       </c>
       <c r="M789" s="2" t="n">
-        <v>40530.33</v>
+        <v>40331.05</v>
       </c>
     </row>
     <row r="790">
@@ -48645,7 +48645,7 @@
         </is>
       </c>
       <c r="M790" s="2" t="n">
-        <v>164933.44</v>
+        <v>164122.49</v>
       </c>
     </row>
     <row r="791">
@@ -48706,7 +48706,7 @@
         </is>
       </c>
       <c r="M791" s="2" t="n">
-        <v>49490.26</v>
+        <v>49246.92</v>
       </c>
     </row>
     <row r="792">
@@ -48767,7 +48767,7 @@
         </is>
       </c>
       <c r="M792" s="2" t="n">
-        <v>36632.98</v>
+        <v>36452.87</v>
       </c>
     </row>
     <row r="793">
@@ -48828,7 +48828,7 @@
         </is>
       </c>
       <c r="M793" s="2" t="n">
-        <v>1026.79</v>
+        <v>1021.75</v>
       </c>
     </row>
     <row r="794">
@@ -48889,7 +48889,7 @@
         </is>
       </c>
       <c r="M794" s="2" t="n">
-        <v>75785.05</v>
+        <v>75412.44</v>
       </c>
     </row>
     <row r="795">
@@ -48950,7 +48950,7 @@
         </is>
       </c>
       <c r="M795" s="2" t="n">
-        <v>647.8200000000001</v>
+        <v>644.64</v>
       </c>
     </row>
     <row r="796">
@@ -49011,7 +49011,7 @@
         </is>
       </c>
       <c r="M796" s="2" t="n">
-        <v>3638</v>
+        <v>3620.11</v>
       </c>
     </row>
     <row r="797">
@@ -49072,7 +49072,7 @@
         </is>
       </c>
       <c r="M797" s="2" t="n">
-        <v>7654.7</v>
+        <v>7617.06</v>
       </c>
     </row>
     <row r="798">
@@ -49133,7 +49133,7 @@
         </is>
       </c>
       <c r="M798" s="2" t="n">
-        <v>488.67</v>
+        <v>486.27</v>
       </c>
     </row>
     <row r="799">
@@ -49194,7 +49194,7 @@
         </is>
       </c>
       <c r="M799" s="2" t="n">
-        <v>15810.21</v>
+        <v>15732.47</v>
       </c>
     </row>
     <row r="800">
@@ -49255,7 +49255,7 @@
         </is>
       </c>
       <c r="M800" s="2" t="n">
-        <v>8117.68</v>
+        <v>8077.76</v>
       </c>
     </row>
     <row r="801">
@@ -49316,7 +49316,7 @@
         </is>
       </c>
       <c r="M801" s="2" t="n">
-        <v>55147.78</v>
+        <v>54876.63</v>
       </c>
     </row>
     <row r="802">
@@ -49377,7 +49377,7 @@
         </is>
       </c>
       <c r="M802" s="2" t="n">
-        <v>227.55</v>
+        <v>229.08</v>
       </c>
     </row>
     <row r="803">
@@ -49438,7 +49438,7 @@
         </is>
       </c>
       <c r="M803" s="2" t="n">
-        <v>328.16</v>
+        <v>330.36</v>
       </c>
     </row>
     <row r="804">
@@ -49499,7 +49499,7 @@
         </is>
       </c>
       <c r="M804" s="2" t="n">
-        <v>16367.86</v>
+        <v>16477.42</v>
       </c>
     </row>
     <row r="805">
@@ -49560,7 +49560,7 @@
         </is>
       </c>
       <c r="M805" s="2" t="n">
-        <v>13434.65</v>
+        <v>13524.58</v>
       </c>
     </row>
     <row r="806">
@@ -49621,7 +49621,7 @@
         </is>
       </c>
       <c r="M806" s="2" t="n">
-        <v>37375.38</v>
+        <v>37625.56</v>
       </c>
     </row>
     <row r="807">
@@ -49682,7 +49682,7 @@
         </is>
       </c>
       <c r="M807" s="2" t="n">
-        <v>2106.28</v>
+        <v>2120.38</v>
       </c>
     </row>
     <row r="808">
@@ -49743,7 +49743,7 @@
         </is>
       </c>
       <c r="M808" s="2" t="n">
-        <v>23469.16</v>
+        <v>23626.25</v>
       </c>
     </row>
     <row r="809">
@@ -49804,7 +49804,7 @@
         </is>
       </c>
       <c r="M809" s="2" t="n">
-        <v>284.47</v>
+        <v>286.37</v>
       </c>
     </row>
     <row r="810">
@@ -49865,7 +49865,7 @@
         </is>
       </c>
       <c r="M810" s="2" t="n">
-        <v>1173.24</v>
+        <v>1181.1</v>
       </c>
     </row>
     <row r="811">
@@ -49926,7 +49926,7 @@
         </is>
       </c>
       <c r="M811" s="2" t="n">
-        <v>34739.6</v>
+        <v>34972.13</v>
       </c>
     </row>
     <row r="812">
@@ -49987,7 +49987,7 @@
         </is>
       </c>
       <c r="M812" s="2" t="n">
-        <v>6866.43</v>
+        <v>6912.39</v>
       </c>
     </row>
     <row r="813">
@@ -50048,7 +50048,7 @@
         </is>
       </c>
       <c r="M813" s="2" t="n">
-        <v>14711.1</v>
+        <v>14809.57</v>
       </c>
     </row>
     <row r="814">
@@ -50109,7 +50109,7 @@
         </is>
       </c>
       <c r="M814" s="2" t="n">
-        <v>2720.39</v>
+        <v>2738.6</v>
       </c>
     </row>
     <row r="815">
@@ -50170,7 +50170,7 @@
         </is>
       </c>
       <c r="M815" s="2" t="n">
-        <v>8812.51</v>
+        <v>8871.5</v>
       </c>
     </row>
     <row r="816">
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="M816" s="2" t="n">
-        <v>10535.12</v>
+        <v>10605.64</v>
       </c>
     </row>
     <row r="817">
@@ -50292,7 +50292,7 @@
         </is>
       </c>
       <c r="M817" s="2" t="n">
-        <v>713.89</v>
+        <v>718.67</v>
       </c>
     </row>
     <row r="818">
@@ -50353,7 +50353,7 @@
         </is>
       </c>
       <c r="M818" s="2" t="n">
-        <v>8310.02</v>
+        <v>8365.65</v>
       </c>
     </row>
     <row r="819">
@@ -50414,7 +50414,7 @@
         </is>
       </c>
       <c r="M819" s="2" t="n">
-        <v>9534.92</v>
+        <v>9598.74</v>
       </c>
     </row>
     <row r="820">
@@ -50475,7 +50475,7 @@
         </is>
       </c>
       <c r="M820" s="2" t="n">
-        <v>19431.37</v>
+        <v>19561.43</v>
       </c>
     </row>
     <row r="821">
@@ -50536,7 +50536,7 @@
         </is>
       </c>
       <c r="M821" s="2" t="n">
-        <v>4109.02</v>
+        <v>4136.52</v>
       </c>
     </row>
     <row r="822">
@@ -50597,7 +50597,7 @@
         </is>
       </c>
       <c r="M822" s="2" t="n">
-        <v>590.24</v>
+        <v>594.1900000000001</v>
       </c>
     </row>
     <row r="823">
@@ -50658,7 +50658,7 @@
         </is>
       </c>
       <c r="M823" s="2" t="n">
-        <v>8310.02</v>
+        <v>8365.65</v>
       </c>
     </row>
     <row r="824">
@@ -50719,7 +50719,7 @@
         </is>
       </c>
       <c r="M824" s="2" t="n">
-        <v>38218.69</v>
+        <v>38474.5</v>
       </c>
     </row>
     <row r="825">
@@ -50780,7 +50780,7 @@
         </is>
       </c>
       <c r="M825" s="2" t="n">
-        <v>152.84</v>
+        <v>153.86</v>
       </c>
     </row>
     <row r="826">
@@ -50841,7 +50841,7 @@
         </is>
       </c>
       <c r="M826" s="2" t="n">
-        <v>8183.93</v>
+        <v>8238.709999999999</v>
       </c>
     </row>
     <row r="827">
@@ -50902,7 +50902,7 @@
         </is>
       </c>
       <c r="M827" s="2" t="n">
-        <v>1036.21</v>
+        <v>1043.14</v>
       </c>
     </row>
     <row r="828">
@@ -50963,7 +50963,7 @@
         </is>
       </c>
       <c r="M828" s="2" t="n">
-        <v>423.53</v>
+        <v>426.37</v>
       </c>
     </row>
     <row r="829">
@@ -51024,7 +51024,7 @@
         </is>
       </c>
       <c r="M829" s="2" t="n">
-        <v>25048.81</v>
+        <v>25216.47</v>
       </c>
     </row>
     <row r="830">
@@ -51085,7 +51085,7 @@
         </is>
       </c>
       <c r="M830" s="2" t="n">
-        <v>529.91</v>
+        <v>533.45</v>
       </c>
     </row>
     <row r="831">
@@ -51146,7 +51146,7 @@
         </is>
       </c>
       <c r="M831" s="2" t="n">
-        <v>1275.8</v>
+        <v>1284.34</v>
       </c>
     </row>
     <row r="832">
@@ -51207,7 +51207,7 @@
         </is>
       </c>
       <c r="M832" s="2" t="n">
-        <v>7731.13</v>
+        <v>7782.88</v>
       </c>
     </row>
     <row r="833">
@@ -51268,7 +51268,7 @@
         </is>
       </c>
       <c r="M833" s="2" t="n">
-        <v>121.18</v>
+        <v>121.99</v>
       </c>
     </row>
     <row r="834">
@@ -51329,7 +51329,7 @@
         </is>
       </c>
       <c r="M834" s="2" t="n">
-        <v>10269.35</v>
+        <v>10338.09</v>
       </c>
     </row>
     <row r="835">
@@ -51390,7 +51390,7 @@
         </is>
       </c>
       <c r="M835" s="2" t="n">
-        <v>8183.93</v>
+        <v>8238.709999999999</v>
       </c>
     </row>
     <row r="836">
@@ -51451,7 +51451,7 @@
         </is>
       </c>
       <c r="M836" s="2" t="n">
-        <v>9488.309999999999</v>
+        <v>9551.82</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/jul-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/jul-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jul-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jul-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -564,7 +564,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16417,7 +16417,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -19284,7 +19284,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -20382,7 +20382,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -24957,7 +24957,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -25079,7 +25079,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -28495,7 +28495,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -31911,7 +31911,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -47832,7 +47832,7 @@
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I777" t="inlineStr">

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/jul-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/jul-2026.xlsx
@@ -627,7 +627,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -810,7 +814,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -871,7 +879,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1054,7 +1066,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1176,7 +1192,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1237,7 +1257,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1359,7 +1383,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1603,7 +1631,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1725,7 +1757,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1973,7 +2009,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2217,7 +2257,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2461,7 +2505,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2522,7 +2570,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2705,7 +2757,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2949,7 +3005,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3193,7 +3253,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3315,7 +3379,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3437,7 +3505,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3559,7 +3631,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3742,7 +3818,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3803,7 +3883,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3986,7 +4070,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4047,7 +4135,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4169,7 +4261,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4230,7 +4326,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4413,7 +4513,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4474,7 +4578,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4535,7 +4643,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4596,7 +4708,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4657,7 +4773,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4779,7 +4899,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4901,7 +5025,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4962,7 +5090,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5084,7 +5216,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5145,7 +5281,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5206,7 +5346,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5267,7 +5411,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5328,7 +5476,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5389,7 +5541,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5572,7 +5728,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5633,7 +5793,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5694,7 +5858,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5816,7 +5984,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6182,7 +6354,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6670,7 +6846,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6731,7 +6911,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6792,7 +6976,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6853,7 +7041,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7097,7 +7289,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7158,7 +7354,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7402,7 +7602,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7524,7 +7728,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7646,7 +7854,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7768,7 +7980,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7890,7 +8106,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8012,7 +8232,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8073,7 +8297,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8134,7 +8362,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8439,7 +8671,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8500,7 +8736,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8927,7 +9167,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8988,7 +9232,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9110,7 +9358,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9171,7 +9423,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9415,7 +9671,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9476,7 +9736,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9598,7 +9862,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9659,7 +9927,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9903,7 +10175,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9964,7 +10240,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10025,7 +10305,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10391,7 +10675,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10574,7 +10862,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10635,7 +10927,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10757,7 +11053,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10818,7 +11118,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11184,7 +11488,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11245,7 +11553,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11550,7 +11862,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12099,7 +12415,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12221,7 +12541,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12648,7 +12972,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12709,7 +13037,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12770,7 +13102,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12953,7 +13289,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13014,7 +13354,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13136,7 +13480,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13258,7 +13606,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13319,7 +13671,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13441,7 +13797,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13502,7 +13862,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13563,7 +13927,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13624,7 +13992,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13685,7 +14057,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13746,7 +14122,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13807,7 +14187,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13868,7 +14252,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13929,7 +14317,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14356,7 +14748,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14417,7 +14813,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14539,7 +14939,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14600,7 +15004,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14844,7 +15252,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14905,7 +15317,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15149,7 +15565,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15271,7 +15691,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15393,7 +15817,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15454,7 +15882,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15515,7 +15947,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15576,7 +16012,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15637,7 +16077,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15698,7 +16142,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15759,7 +16207,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15820,7 +16272,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15881,7 +16337,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15942,7 +16402,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16003,7 +16467,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16064,7 +16532,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16369,7 +16841,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16430,7 +16906,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16491,7 +16971,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16857,7 +17341,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17223,7 +17711,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17345,7 +17837,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17406,7 +17902,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17467,7 +17967,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17589,7 +18093,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17650,7 +18158,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17711,7 +18223,11 @@
           <t>77.358.747-7</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17772,7 +18288,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18016,7 +18536,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18138,7 +18662,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18260,7 +18788,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18321,7 +18853,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18443,7 +18979,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18504,7 +19044,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18565,7 +19109,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18748,7 +19296,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18809,7 +19361,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18870,7 +19426,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18931,7 +19491,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19053,7 +19617,11 @@
           <t>77.544.929-2</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19114,7 +19682,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19175,7 +19747,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19236,7 +19812,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19297,7 +19877,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19358,7 +19942,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19480,7 +20068,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19724,7 +20316,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19846,7 +20442,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20029,7 +20629,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20090,7 +20694,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20395,7 +21003,11 @@
           <t>77.544.929-2</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20456,7 +21068,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20517,7 +21133,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20639,7 +21259,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20761,7 +21385,11 @@
           <t>78.616.370-6</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20944,7 +21572,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21005,7 +21637,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21066,7 +21702,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21127,7 +21767,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21310,7 +21954,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21371,7 +22019,11 @@
           <t>77.544.929-2</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21432,7 +22084,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21493,7 +22149,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21554,7 +22214,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21859,7 +22523,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22103,7 +22771,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22591,7 +23263,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22713,7 +23389,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22835,7 +23515,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22896,7 +23580,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22957,7 +23645,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23018,7 +23710,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23079,7 +23775,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23140,7 +23840,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23262,7 +23966,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23445,7 +24153,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23506,7 +24218,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23628,7 +24344,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23811,7 +24531,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23872,7 +24596,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23933,7 +24661,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23994,7 +24726,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24055,7 +24791,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24116,7 +24856,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24177,7 +24921,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24360,7 +25108,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24909,7 +25661,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24970,7 +25726,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25092,7 +25852,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25214,7 +25978,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25763,7 +26531,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25824,7 +26596,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26190,7 +26966,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26251,7 +27031,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26495,7 +27279,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26678,7 +27466,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26922,7 +27714,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26983,7 +27779,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27166,7 +27966,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27288,7 +28092,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27715,7 +28523,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27776,7 +28588,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28081,7 +28897,11 @@
           <t>77.942.697-1</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28264,7 +29084,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28325,7 +29149,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28386,7 +29214,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28447,7 +29279,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28996,7 +29832,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29301,7 +30141,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29484,7 +30328,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29545,7 +30393,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29606,7 +30458,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29789,7 +30645,11 @@
           <t>77.942.697-1</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29911,7 +30771,11 @@
           <t>77.544.929-2</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29972,7 +30836,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30277,7 +31145,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30460,7 +31332,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30765,7 +31641,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30887,7 +31767,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30948,7 +31832,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31009,7 +31897,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31070,7 +31962,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31131,7 +32027,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31253,7 +32153,11 @@
           <t>78.616.370-6</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31314,7 +32218,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31558,7 +32466,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31741,7 +32653,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31802,7 +32718,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31924,7 +32844,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31985,7 +32909,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32046,7 +32974,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32168,7 +33100,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32229,7 +33165,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32290,7 +33230,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32351,7 +33295,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32412,7 +33360,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32717,7 +33669,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32839,7 +33795,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33083,7 +34043,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33205,7 +34169,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33266,7 +34234,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33327,7 +34299,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33449,7 +34425,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33510,7 +34490,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33571,7 +34555,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33693,7 +34681,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33754,7 +34746,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33876,7 +34872,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33937,7 +34937,11 @@
           <t>77.544.929-2</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34120,7 +35124,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34242,7 +35250,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34425,7 +35437,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34486,7 +35502,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34547,7 +35567,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34608,7 +35632,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34791,7 +35819,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34852,7 +35884,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34913,7 +35949,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35035,7 +36075,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35157,7 +36201,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35584,7 +36632,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35828,7 +36880,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35889,7 +36945,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36011,7 +37071,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36194,7 +37258,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36255,7 +37323,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36438,7 +37510,11 @@
           <t>77.544.929-2</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36499,7 +37575,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36743,7 +37823,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36865,7 +37949,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36926,7 +38014,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36987,7 +38079,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37048,7 +38144,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37109,7 +38209,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37170,7 +38274,11 @@
           <t>76.102.347-0</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37231,7 +38339,11 @@
           <t>77.544.929-2</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37292,7 +38404,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37963,7 +39079,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38024,7 +39144,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38146,7 +39270,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38207,7 +39335,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38329,7 +39461,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38634,7 +39770,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38817,7 +39957,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38878,7 +40022,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39000,7 +40148,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39061,7 +40213,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39305,7 +40461,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39366,7 +40526,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39488,7 +40652,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39610,7 +40778,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39671,7 +40843,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39732,7 +40908,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39976,7 +41156,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40098,7 +41282,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40342,7 +41530,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40403,7 +41595,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40464,7 +41660,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40708,7 +41908,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40952,7 +42156,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41013,7 +42221,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41074,7 +42286,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L666" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41318,7 +42534,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41562,7 +42782,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41623,7 +42847,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L675" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41684,7 +42912,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K676" t="inlineStr"/>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L676" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41867,7 +43099,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41928,7 +43164,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K680" t="inlineStr"/>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L680" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42111,7 +43351,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L683" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42172,7 +43416,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K684" t="inlineStr"/>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L684" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42233,7 +43481,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K685" t="inlineStr"/>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L685" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42416,7 +43668,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L688" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42538,7 +43794,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K690" t="inlineStr"/>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L690" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42660,7 +43920,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K692" t="inlineStr"/>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42904,7 +44168,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K696" t="inlineStr"/>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L696" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42965,7 +44233,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K697" t="inlineStr"/>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L697" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43026,7 +44298,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K698" t="inlineStr"/>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L698" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43148,7 +44424,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L700" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43270,7 +44550,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K702" t="inlineStr"/>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L702" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43331,7 +44615,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K703" t="inlineStr"/>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L703" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43392,7 +44680,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K704" t="inlineStr"/>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L704" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43636,7 +44928,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K708" t="inlineStr"/>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L708" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43697,7 +44993,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K709" t="inlineStr"/>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L709" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43819,7 +45119,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K711" t="inlineStr"/>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L711" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43880,7 +45184,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K712" t="inlineStr"/>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L712" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44002,7 +45310,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K714" t="inlineStr"/>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L714" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44185,7 +45497,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K717" t="inlineStr"/>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L717" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44307,7 +45623,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K719" t="inlineStr"/>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L719" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44490,7 +45810,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K722" t="inlineStr"/>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L722" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44551,7 +45875,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K723" t="inlineStr"/>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L723" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44612,7 +45940,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K724" t="inlineStr"/>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L724" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44795,7 +46127,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K727" t="inlineStr"/>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L727" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44856,7 +46192,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K728" t="inlineStr"/>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L728" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44978,7 +46318,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K730" t="inlineStr"/>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L730" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45039,7 +46383,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K731" t="inlineStr"/>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L731" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45100,7 +46448,11 @@
           <t>77.544.929-2</t>
         </is>
       </c>
-      <c r="K732" t="inlineStr"/>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L732" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45161,7 +46513,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K733" t="inlineStr"/>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L733" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45222,7 +46578,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K734" t="inlineStr"/>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L734" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45344,7 +46704,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K736" t="inlineStr"/>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L736" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45466,7 +46830,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K738" t="inlineStr"/>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L738" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45771,7 +47139,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K743" t="inlineStr"/>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L743" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45832,7 +47204,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K744" t="inlineStr"/>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L744" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45893,7 +47269,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K745" t="inlineStr"/>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L745" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46076,7 +47456,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K748" t="inlineStr"/>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L748" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46137,7 +47521,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K749" t="inlineStr"/>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L749" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46198,7 +47586,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K750" t="inlineStr"/>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L750" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46259,7 +47651,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K751" t="inlineStr"/>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L751" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46320,7 +47716,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K752" t="inlineStr"/>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L752" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46381,7 +47781,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K753" t="inlineStr"/>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L753" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46442,7 +47846,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K754" t="inlineStr"/>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L754" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46503,7 +47911,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K755" t="inlineStr"/>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L755" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46625,7 +48037,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K757" t="inlineStr"/>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L757" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46747,7 +48163,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K759" t="inlineStr"/>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L759" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46869,7 +48289,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K761" t="inlineStr"/>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L761" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47052,7 +48476,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K764" t="inlineStr"/>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L764" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47174,7 +48602,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K766" t="inlineStr"/>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L766" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47235,7 +48667,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K767" t="inlineStr"/>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L767" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47296,7 +48732,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K768" t="inlineStr"/>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L768" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47357,7 +48797,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K769" t="inlineStr"/>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L769" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47418,7 +48862,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K770" t="inlineStr"/>
+      <c r="K770" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L770" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47601,7 +49049,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K773" t="inlineStr"/>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L773" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47723,7 +49175,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K775" t="inlineStr"/>
+      <c r="K775" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L775" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47906,7 +49362,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K778" t="inlineStr"/>
+      <c r="K778" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L778" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47967,7 +49427,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K779" t="inlineStr"/>
+      <c r="K779" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L779" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48272,7 +49736,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K784" t="inlineStr"/>
+      <c r="K784" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L784" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48333,7 +49801,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K785" t="inlineStr"/>
+      <c r="K785" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L785" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48638,7 +50110,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K790" t="inlineStr"/>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L790" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48699,7 +50175,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K791" t="inlineStr"/>
+      <c r="K791" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L791" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48760,7 +50240,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K792" t="inlineStr"/>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L792" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48882,7 +50366,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K794" t="inlineStr"/>
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L794" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49126,7 +50614,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K798" t="inlineStr"/>
+      <c r="K798" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L798" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49187,7 +50679,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K799" t="inlineStr"/>
+      <c r="K799" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L799" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49370,7 +50866,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K802" t="inlineStr"/>
+      <c r="K802" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L802" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49492,7 +50992,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K804" t="inlineStr"/>
+      <c r="K804" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L804" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49553,7 +51057,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K805" t="inlineStr"/>
+      <c r="K805" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L805" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49614,7 +51122,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K806" t="inlineStr"/>
+      <c r="K806" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L806" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49675,7 +51187,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K807" t="inlineStr"/>
+      <c r="K807" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L807" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49736,7 +51252,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K808" t="inlineStr"/>
+      <c r="K808" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L808" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49919,7 +51439,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K811" t="inlineStr"/>
+      <c r="K811" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L811" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49980,7 +51504,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K812" t="inlineStr"/>
+      <c r="K812" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L812" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50041,7 +51569,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K813" t="inlineStr"/>
+      <c r="K813" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L813" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50102,7 +51634,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K814" t="inlineStr"/>
+      <c r="K814" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L814" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50163,7 +51699,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K815" t="inlineStr"/>
+      <c r="K815" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L815" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50224,7 +51764,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K816" t="inlineStr"/>
+      <c r="K816" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L816" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50346,7 +51890,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K818" t="inlineStr"/>
+      <c r="K818" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L818" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50468,7 +52016,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K820" t="inlineStr"/>
+      <c r="K820" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L820" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50651,7 +52203,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K823" t="inlineStr"/>
+      <c r="K823" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L823" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50834,7 +52390,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K826" t="inlineStr"/>
+      <c r="K826" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L826" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51017,7 +52577,11 @@
           <t>78.616.370-6</t>
         </is>
       </c>
-      <c r="K829" t="inlineStr"/>
+      <c r="K829" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L829" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51139,7 +52703,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K831" t="inlineStr"/>
+      <c r="K831" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L831" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51200,7 +52768,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K832" t="inlineStr"/>
+      <c r="K832" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L832" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51322,7 +52894,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K834" t="inlineStr"/>
+      <c r="K834" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L834" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51383,7 +52959,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K835" t="inlineStr"/>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L835" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51444,7 +53024,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K836" t="inlineStr"/>
+      <c r="K836" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L836" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51993,7 +53577,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K845" t="inlineStr"/>
+      <c r="K845" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L845" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52115,7 +53703,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K847" t="inlineStr"/>
+      <c r="K847" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L847" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52176,7 +53768,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K848" t="inlineStr"/>
+      <c r="K848" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L848" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52237,7 +53833,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K849" t="inlineStr"/>
+      <c r="K849" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L849" t="inlineStr">
         <is>
           <t>USD</t>
